--- a/validation/validation_ground_truth_CS.xlsx
+++ b/validation/validation_ground_truth_CS.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1296" documentId="11_F25DC773A252ABDACC104898899A5BBC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E39F3E-83E5-4269-829C-0F64866D2F54}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VA#11541" sheetId="2" r:id="rId1"/>
@@ -711,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
@@ -728,15 +728,14 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1046,7 +1045,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -1060,7 +1059,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
+      <c r="A3" s="14"/>
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -1072,7 +1071,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="14"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -1081,7 +1080,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="14"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1093,7 +1092,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+      <c r="A6" s="14"/>
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -1105,7 +1104,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
+      <c r="A7" s="14"/>
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -1117,7 +1116,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1133,7 +1132,7 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="5" t="s">
         <v>122</v>
       </c>
@@ -1147,7 +1146,7 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
@@ -1161,7 +1160,7 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
@@ -1175,21 +1174,21 @@
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>155</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
@@ -1203,7 +1202,7 @@
       <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
@@ -1217,7 +1216,7 @@
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
@@ -1231,7 +1230,7 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
@@ -1245,7 +1244,7 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="5" t="s">
         <v>24</v>
       </c>
@@ -1259,7 +1258,7 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="5" t="s">
         <v>158</v>
       </c>
@@ -1273,7 +1272,7 @@
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="5" t="s">
         <v>26</v>
       </c>
@@ -1287,7 +1286,7 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="5" t="s">
         <v>179</v>
       </c>
@@ -1301,7 +1300,7 @@
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="5" t="s">
         <v>28</v>
       </c>
@@ -1315,7 +1314,7 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
@@ -1329,7 +1328,7 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="5" t="s">
         <v>31</v>
       </c>
@@ -1343,7 +1342,7 @@
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="5" t="s">
         <v>32</v>
       </c>
@@ -1357,7 +1356,7 @@
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
@@ -1371,7 +1370,7 @@
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -1385,7 +1384,7 @@
       <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
@@ -1399,7 +1398,7 @@
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -1413,7 +1412,7 @@
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -1427,7 +1426,7 @@
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
@@ -1441,7 +1440,7 @@
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
@@ -1455,7 +1454,7 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="5" t="s">
         <v>40</v>
       </c>
@@ -1469,7 +1468,7 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="5" t="s">
         <v>41</v>
       </c>
@@ -1483,7 +1482,7 @@
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="5" t="s">
         <v>42</v>
       </c>
@@ -1497,7 +1496,7 @@
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
@@ -1539,7 +1538,7 @@
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B38" t="s">
@@ -1553,7 +1552,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
+      <c r="A39" s="14"/>
       <c r="B39" t="s">
         <v>122</v>
       </c>
@@ -1565,7 +1564,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
+      <c r="A40" s="14"/>
       <c r="B40" t="s">
         <v>59</v>
       </c>
@@ -1577,7 +1576,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
+      <c r="A41" s="14"/>
       <c r="B41" t="s">
         <v>16</v>
       </c>
@@ -1589,19 +1588,19 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
+      <c r="A42" s="14"/>
       <c r="B42" t="s">
         <v>18</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="12" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
+      <c r="A43" s="14"/>
       <c r="B43" t="s">
         <v>20</v>
       </c>
@@ -1613,7 +1612,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
+      <c r="A44" s="14"/>
       <c r="B44" t="s">
         <v>21</v>
       </c>
@@ -1625,7 +1624,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
+      <c r="A45" s="14"/>
       <c r="B45" t="s">
         <v>22</v>
       </c>
@@ -1637,7 +1636,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
+      <c r="A46" s="14"/>
       <c r="B46" t="s">
         <v>23</v>
       </c>
@@ -1649,7 +1648,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+      <c r="A47" s="14"/>
       <c r="B47" t="s">
         <v>24</v>
       </c>
@@ -1661,8 +1660,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
-      <c r="B48" s="15" t="s">
+      <c r="A48" s="14"/>
+      <c r="B48" t="s">
         <v>158</v>
       </c>
       <c r="C48" t="s">
@@ -1673,7 +1672,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+      <c r="A49" s="14"/>
       <c r="B49" t="s">
         <v>26</v>
       </c>
@@ -1685,7 +1684,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+      <c r="A50" s="14"/>
       <c r="B50" t="s">
         <v>179</v>
       </c>
@@ -1697,7 +1696,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+      <c r="A51" s="14"/>
       <c r="B51" t="s">
         <v>48</v>
       </c>
@@ -1709,7 +1708,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+      <c r="A52" s="14"/>
       <c r="B52" t="s">
         <v>29</v>
       </c>
@@ -1721,7 +1720,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="14"/>
       <c r="B53" t="s">
         <v>49</v>
       </c>
@@ -1733,7 +1732,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
+      <c r="A54" s="14"/>
       <c r="B54" t="s">
         <v>32</v>
       </c>
@@ -1745,7 +1744,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+      <c r="A55" s="14"/>
       <c r="B55" t="s">
         <v>33</v>
       </c>
@@ -1757,7 +1756,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+      <c r="A56" s="14"/>
       <c r="B56" t="s">
         <v>34</v>
       </c>
@@ -1769,7 +1768,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+      <c r="A57" s="14"/>
       <c r="B57" t="s">
         <v>35</v>
       </c>
@@ -1781,7 +1780,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+      <c r="A58" s="14"/>
       <c r="B58" t="s">
         <v>36</v>
       </c>
@@ -1793,7 +1792,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+      <c r="A59" s="14"/>
       <c r="B59" t="s">
         <v>50</v>
       </c>
@@ -1805,7 +1804,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
+      <c r="A60" s="14"/>
       <c r="B60" t="s">
         <v>38</v>
       </c>
@@ -1817,7 +1816,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+      <c r="A61" s="14"/>
       <c r="B61" t="s">
         <v>39</v>
       </c>
@@ -1829,7 +1828,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
+      <c r="A62" s="14"/>
       <c r="B62" t="s">
         <v>40</v>
       </c>
@@ -1841,7 +1840,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
+      <c r="A63" s="14"/>
       <c r="B63" t="s">
         <v>41</v>
       </c>
@@ -1853,7 +1852,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
+      <c r="A64" s="14"/>
       <c r="B64" t="s">
         <v>42</v>
       </c>
@@ -1865,7 +1864,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
+      <c r="A65" s="14"/>
       <c r="B65" t="s">
         <v>43</v>
       </c>
@@ -1901,7 +1900,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="15" t="s">
         <v>60</v>
       </c>
       <c r="B68" s="5" t="s">
@@ -1917,7 +1916,7 @@
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="5" t="s">
         <v>122</v>
       </c>
@@ -1931,7 +1930,7 @@
       <c r="F69" s="5"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="13"/>
+      <c r="A70" s="15"/>
       <c r="B70" s="5" t="s">
         <v>59</v>
       </c>
@@ -1943,7 +1942,7 @@
       <c r="F70" s="5"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="5" t="s">
         <v>16</v>
       </c>
@@ -1957,7 +1956,7 @@
       <c r="F71" s="5"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="5" t="s">
         <v>18</v>
       </c>
@@ -1971,7 +1970,7 @@
       <c r="F72" s="5"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="5" t="s">
         <v>20</v>
       </c>
@@ -1985,7 +1984,7 @@
       <c r="F73" s="5"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
+      <c r="A74" s="15"/>
       <c r="B74" s="5" t="s">
         <v>21</v>
       </c>
@@ -1999,7 +1998,7 @@
       <c r="F74" s="5"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
+      <c r="A75" s="15"/>
       <c r="B75" s="5" t="s">
         <v>22</v>
       </c>
@@ -2013,7 +2012,7 @@
       <c r="F75" s="5"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="5" t="s">
         <v>23</v>
       </c>
@@ -2027,7 +2026,7 @@
       <c r="F76" s="5"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
+      <c r="A77" s="15"/>
       <c r="B77" s="5" t="s">
         <v>24</v>
       </c>
@@ -2041,7 +2040,7 @@
       <c r="F77" s="5"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
+      <c r="A78" s="15"/>
       <c r="B78" s="5" t="s">
         <v>158</v>
       </c>
@@ -2055,7 +2054,7 @@
       <c r="F78" s="5"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="5" t="s">
         <v>26</v>
       </c>
@@ -2069,7 +2068,7 @@
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
+      <c r="A80" s="15"/>
       <c r="B80" s="5" t="s">
         <v>179</v>
       </c>
@@ -2083,7 +2082,7 @@
       <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
+      <c r="A81" s="15"/>
       <c r="B81" s="5" t="s">
         <v>48</v>
       </c>
@@ -2097,7 +2096,7 @@
       <c r="F81" s="5"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
+      <c r="A82" s="15"/>
       <c r="B82" s="5" t="s">
         <v>29</v>
       </c>
@@ -2111,7 +2110,7 @@
       <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
+      <c r="A83" s="15"/>
       <c r="B83" s="5" t="s">
         <v>49</v>
       </c>
@@ -2125,7 +2124,7 @@
       <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
+      <c r="A84" s="15"/>
       <c r="B84" s="5" t="s">
         <v>32</v>
       </c>
@@ -2139,7 +2138,7 @@
       <c r="F84" s="5"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
+      <c r="A85" s="15"/>
       <c r="B85" s="5" t="s">
         <v>33</v>
       </c>
@@ -2153,7 +2152,7 @@
       <c r="F85" s="5"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
+      <c r="A86" s="15"/>
       <c r="B86" s="5" t="s">
         <v>34</v>
       </c>
@@ -2167,7 +2166,7 @@
       <c r="F86" s="5"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
+      <c r="A87" s="15"/>
       <c r="B87" s="5" t="s">
         <v>35</v>
       </c>
@@ -2181,7 +2180,7 @@
       <c r="F87" s="5"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
+      <c r="A88" s="15"/>
       <c r="B88" s="5" t="s">
         <v>36</v>
       </c>
@@ -2195,7 +2194,7 @@
       <c r="F88" s="5"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="13"/>
+      <c r="A89" s="15"/>
       <c r="B89" s="5" t="s">
         <v>50</v>
       </c>
@@ -2209,7 +2208,7 @@
       <c r="F89" s="5"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="13"/>
+      <c r="A90" s="15"/>
       <c r="B90" s="5" t="s">
         <v>38</v>
       </c>
@@ -2223,7 +2222,7 @@
       <c r="F90" s="5"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="13"/>
+      <c r="A91" s="15"/>
       <c r="B91" s="5" t="s">
         <v>39</v>
       </c>
@@ -2237,7 +2236,7 @@
       <c r="F91" s="5"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="13"/>
+      <c r="A92" s="15"/>
       <c r="B92" s="5" t="s">
         <v>40</v>
       </c>
@@ -2251,7 +2250,7 @@
       <c r="F92" s="5"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="13"/>
+      <c r="A93" s="15"/>
       <c r="B93" s="5" t="s">
         <v>41</v>
       </c>
@@ -2265,7 +2264,7 @@
       <c r="F93" s="5"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="13"/>
+      <c r="A94" s="15"/>
       <c r="B94" s="5" t="s">
         <v>42</v>
       </c>
@@ -2279,7 +2278,7 @@
       <c r="F94" s="5"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="13"/>
+      <c r="A95" s="15"/>
       <c r="B95" s="5" t="s">
         <v>43</v>
       </c>
@@ -2344,7 +2343,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -2364,7 +2363,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
+      <c r="A2" s="14"/>
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -2376,7 +2375,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
+      <c r="A3" s="14"/>
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -2388,7 +2387,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="14"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -2400,7 +2399,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="14"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -2412,7 +2411,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+      <c r="A6" s="14"/>
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -2424,7 +2423,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
+      <c r="A7" s="14"/>
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -2436,7 +2435,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -2452,7 +2451,7 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="5" t="s">
         <v>122</v>
       </c>
@@ -2466,7 +2465,7 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
@@ -2480,7 +2479,7 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
@@ -2494,7 +2493,7 @@
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
@@ -2508,7 +2507,7 @@
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
@@ -2522,7 +2521,7 @@
       <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
@@ -2536,7 +2535,7 @@
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
@@ -2550,7 +2549,7 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
@@ -2564,7 +2563,7 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="5" t="s">
         <v>24</v>
       </c>
@@ -2578,7 +2577,7 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="5" t="s">
         <v>173</v>
       </c>
@@ -2592,7 +2591,7 @@
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="5" t="s">
         <v>26</v>
       </c>
@@ -2606,7 +2605,7 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="5" t="s">
         <v>175</v>
       </c>
@@ -2620,7 +2619,7 @@
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="5" t="s">
         <v>28</v>
       </c>
@@ -2634,7 +2633,7 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
@@ -2648,7 +2647,7 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="5" t="s">
         <v>31</v>
       </c>
@@ -2662,7 +2661,7 @@
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="5" t="s">
         <v>32</v>
       </c>
@@ -2676,7 +2675,7 @@
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
@@ -2690,7 +2689,7 @@
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -2704,7 +2703,7 @@
       <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
@@ -2718,7 +2717,7 @@
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -2732,7 +2731,7 @@
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -2746,35 +2745,35 @@
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="12">
         <v>0.36</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="12">
         <v>0.57999999999999996</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="5" t="s">
         <v>40</v>
       </c>
@@ -2788,7 +2787,7 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="5" t="s">
         <v>41</v>
       </c>
@@ -2802,7 +2801,7 @@
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="5" t="s">
         <v>42</v>
       </c>
@@ -2816,7 +2815,7 @@
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
@@ -2858,7 +2857,7 @@
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B38" t="s">
@@ -2867,12 +2866,12 @@
       <c r="C38" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
+      <c r="A39" s="14"/>
       <c r="B39" t="s">
         <v>121</v>
       </c>
@@ -2884,7 +2883,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
+      <c r="A40" s="14"/>
       <c r="B40" t="s">
         <v>15</v>
       </c>
@@ -2896,7 +2895,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
+      <c r="A41" s="14"/>
       <c r="B41" t="s">
         <v>16</v>
       </c>
@@ -2908,7 +2907,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
+      <c r="A42" s="14"/>
       <c r="B42" t="s">
         <v>18</v>
       </c>
@@ -2920,7 +2919,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
+      <c r="A43" s="14"/>
       <c r="B43" t="s">
         <v>20</v>
       </c>
@@ -2932,7 +2931,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
+      <c r="A44" s="14"/>
       <c r="B44" t="s">
         <v>21</v>
       </c>
@@ -2944,7 +2943,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
+      <c r="A45" s="14"/>
       <c r="B45" t="s">
         <v>22</v>
       </c>
@@ -2956,7 +2955,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
+      <c r="A46" s="14"/>
       <c r="B46" t="s">
         <v>23</v>
       </c>
@@ -2968,7 +2967,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+      <c r="A47" s="14"/>
       <c r="B47" t="s">
         <v>24</v>
       </c>
@@ -2980,7 +2979,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+      <c r="A48" s="14"/>
       <c r="B48" t="s">
         <v>185</v>
       </c>
@@ -2992,7 +2991,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+      <c r="A49" s="14"/>
       <c r="B49" t="s">
         <v>26</v>
       </c>
@@ -3004,7 +3003,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+      <c r="A50" s="14"/>
       <c r="B50" t="s">
         <v>175</v>
       </c>
@@ -3016,7 +3015,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+      <c r="A51" s="14"/>
       <c r="B51" t="s">
         <v>48</v>
       </c>
@@ -3028,7 +3027,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+      <c r="A52" s="14"/>
       <c r="B52" t="s">
         <v>29</v>
       </c>
@@ -3037,7 +3036,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="14"/>
       <c r="B53" t="s">
         <v>49</v>
       </c>
@@ -3049,7 +3048,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
+      <c r="A54" s="14"/>
       <c r="B54" t="s">
         <v>32</v>
       </c>
@@ -3061,7 +3060,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+      <c r="A55" s="14"/>
       <c r="B55" t="s">
         <v>33</v>
       </c>
@@ -3073,7 +3072,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+      <c r="A56" s="14"/>
       <c r="B56" t="s">
         <v>34</v>
       </c>
@@ -3085,7 +3084,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+      <c r="A57" s="14"/>
       <c r="B57" t="s">
         <v>35</v>
       </c>
@@ -3097,7 +3096,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+      <c r="A58" s="14"/>
       <c r="B58" t="s">
         <v>36</v>
       </c>
@@ -3109,7 +3108,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+      <c r="A59" s="14"/>
       <c r="B59" t="s">
         <v>50</v>
       </c>
@@ -3121,31 +3120,31 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
+      <c r="A60" s="14"/>
       <c r="B60" t="s">
         <v>38</v>
       </c>
       <c r="C60" t="s">
         <v>6</v>
       </c>
-      <c r="D60" s="14">
+      <c r="D60" s="12">
         <v>0.17</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+      <c r="A61" s="14"/>
       <c r="B61" t="s">
         <v>39</v>
       </c>
       <c r="C61" t="s">
         <v>6</v>
       </c>
-      <c r="D61" s="14">
+      <c r="D61" s="12">
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
+      <c r="A62" s="14"/>
       <c r="B62" t="s">
         <v>40</v>
       </c>
@@ -3157,7 +3156,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
+      <c r="A63" s="14"/>
       <c r="B63" t="s">
         <v>41</v>
       </c>
@@ -3169,7 +3168,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
+      <c r="A64" s="14"/>
       <c r="B64" t="s">
         <v>42</v>
       </c>
@@ -3181,7 +3180,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
+      <c r="A65" s="14"/>
       <c r="B65" t="s">
         <v>43</v>
       </c>
@@ -3254,7 +3253,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -3268,7 +3267,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
+      <c r="A3" s="14"/>
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -3280,7 +3279,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="14"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -3292,7 +3291,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="14"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -3304,7 +3303,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+      <c r="A6" s="14"/>
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -3316,7 +3315,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
+      <c r="A7" s="14"/>
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -3328,7 +3327,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="15" t="s">
         <v>131</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -3344,7 +3343,7 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="5" t="s">
         <v>122</v>
       </c>
@@ -3358,7 +3357,7 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
@@ -3372,7 +3371,7 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
@@ -3386,7 +3385,7 @@
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
@@ -3400,7 +3399,7 @@
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
@@ -3414,7 +3413,7 @@
       <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
@@ -3428,7 +3427,7 @@
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
@@ -3442,7 +3441,7 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
@@ -3456,7 +3455,7 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="5" t="s">
         <v>24</v>
       </c>
@@ -3470,7 +3469,7 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="5" t="s">
         <v>185</v>
       </c>
@@ -3484,7 +3483,7 @@
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="5" t="s">
         <v>26</v>
       </c>
@@ -3498,7 +3497,7 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="5" t="s">
         <v>194</v>
       </c>
@@ -3512,7 +3511,7 @@
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="5" t="s">
         <v>28</v>
       </c>
@@ -3526,7 +3525,7 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
@@ -3540,7 +3539,7 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="5" t="s">
         <v>31</v>
       </c>
@@ -3554,7 +3553,7 @@
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="5" t="s">
         <v>32</v>
       </c>
@@ -3568,21 +3567,21 @@
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="5">
         <v>53.7</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -3596,21 +3595,21 @@
       <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C27" s="5">
         <v>22</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -3624,21 +3623,21 @@
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="5">
         <v>4.2</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
@@ -3652,7 +3651,7 @@
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
@@ -3666,7 +3665,7 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="5" t="s">
         <v>40</v>
       </c>
@@ -3680,21 +3679,21 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="5">
         <v>1.6</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="5" t="s">
         <v>42</v>
       </c>
@@ -3708,7 +3707,7 @@
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
@@ -3750,7 +3749,7 @@
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="14" t="s">
         <v>132</v>
       </c>
       <c r="B38" t="s">
@@ -3764,7 +3763,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
+      <c r="A39" s="14"/>
       <c r="B39" t="s">
         <v>122</v>
       </c>
@@ -3776,7 +3775,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
+      <c r="A40" s="14"/>
       <c r="B40" t="s">
         <v>59</v>
       </c>
@@ -3788,7 +3787,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
+      <c r="A41" s="14"/>
       <c r="B41" t="s">
         <v>16</v>
       </c>
@@ -3800,7 +3799,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
+      <c r="A42" s="14"/>
       <c r="B42" t="s">
         <v>18</v>
       </c>
@@ -3812,7 +3811,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
+      <c r="A43" s="14"/>
       <c r="B43" t="s">
         <v>20</v>
       </c>
@@ -3824,7 +3823,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
+      <c r="A44" s="14"/>
       <c r="B44" t="s">
         <v>21</v>
       </c>
@@ -3836,7 +3835,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
+      <c r="A45" s="14"/>
       <c r="B45" t="s">
         <v>22</v>
       </c>
@@ -3848,7 +3847,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
+      <c r="A46" s="14"/>
       <c r="B46" t="s">
         <v>23</v>
       </c>
@@ -3860,7 +3859,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+      <c r="A47" s="14"/>
       <c r="B47" t="s">
         <v>24</v>
       </c>
@@ -3872,7 +3871,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+      <c r="A48" s="14"/>
       <c r="B48" t="s">
         <v>185</v>
       </c>
@@ -3884,7 +3883,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+      <c r="A49" s="14"/>
       <c r="B49" t="s">
         <v>26</v>
       </c>
@@ -3896,7 +3895,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+      <c r="A50" s="14"/>
       <c r="B50" t="s">
         <v>194</v>
       </c>
@@ -3908,7 +3907,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+      <c r="A51" s="14"/>
       <c r="B51" t="s">
         <v>48</v>
       </c>
@@ -3920,7 +3919,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+      <c r="A52" s="14"/>
       <c r="B52" t="s">
         <v>29</v>
       </c>
@@ -3932,19 +3931,19 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="14"/>
       <c r="B53" t="s">
         <v>49</v>
       </c>
       <c r="C53">
         <v>500</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="13" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
+      <c r="A54" s="14"/>
       <c r="B54" t="s">
         <v>32</v>
       </c>
@@ -3956,19 +3955,19 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+      <c r="A55" s="14"/>
       <c r="B55" t="s">
         <v>33</v>
       </c>
       <c r="C55">
         <v>53.7</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+      <c r="A56" s="14"/>
       <c r="B56" t="s">
         <v>34</v>
       </c>
@@ -3980,43 +3979,43 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+      <c r="A57" s="14"/>
       <c r="B57" t="s">
         <v>35</v>
       </c>
       <c r="C57">
         <v>22</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+      <c r="A58" s="14"/>
       <c r="B58" t="s">
         <v>36</v>
       </c>
       <c r="C58">
         <v>0.98</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58">
         <v>0.98</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+      <c r="A59" s="14"/>
       <c r="B59" t="s">
         <v>50</v>
       </c>
       <c r="C59">
         <v>4.2</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
+      <c r="A60" s="14"/>
       <c r="B60" t="s">
         <v>38</v>
       </c>
@@ -4028,7 +4027,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+      <c r="A61" s="14"/>
       <c r="B61" t="s">
         <v>39</v>
       </c>
@@ -4040,7 +4039,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
+      <c r="A62" s="14"/>
       <c r="B62" t="s">
         <v>40</v>
       </c>
@@ -4052,19 +4051,19 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
+      <c r="A63" s="14"/>
       <c r="B63" t="s">
         <v>41</v>
       </c>
       <c r="C63">
         <v>1.6</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
+      <c r="A64" s="14"/>
       <c r="B64" t="s">
         <v>42</v>
       </c>
@@ -4076,7 +4075,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
+      <c r="A65" s="14"/>
       <c r="B65" t="s">
         <v>43</v>
       </c>
@@ -4112,7 +4111,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="15" t="s">
         <v>133</v>
       </c>
       <c r="B68" s="5" t="s">
@@ -4128,7 +4127,7 @@
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="5" t="s">
         <v>122</v>
       </c>
@@ -4142,7 +4141,7 @@
       <c r="F69" s="5"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="13"/>
+      <c r="A70" s="15"/>
       <c r="B70" s="5" t="s">
         <v>59</v>
       </c>
@@ -4156,7 +4155,7 @@
       <c r="F70" s="5"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="5" t="s">
         <v>16</v>
       </c>
@@ -4170,7 +4169,7 @@
       <c r="F71" s="5"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="5" t="s">
         <v>18</v>
       </c>
@@ -4184,7 +4183,7 @@
       <c r="F72" s="5"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="5" t="s">
         <v>20</v>
       </c>
@@ -4198,7 +4197,7 @@
       <c r="F73" s="5"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
+      <c r="A74" s="15"/>
       <c r="B74" s="5" t="s">
         <v>21</v>
       </c>
@@ -4212,7 +4211,7 @@
       <c r="F74" s="5"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
+      <c r="A75" s="15"/>
       <c r="B75" s="5" t="s">
         <v>22</v>
       </c>
@@ -4226,7 +4225,7 @@
       <c r="F75" s="5"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="5" t="s">
         <v>23</v>
       </c>
@@ -4240,7 +4239,7 @@
       <c r="F76" s="5"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
+      <c r="A77" s="15"/>
       <c r="B77" s="5" t="s">
         <v>24</v>
       </c>
@@ -4254,7 +4253,7 @@
       <c r="F77" s="5"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
+      <c r="A78" s="15"/>
       <c r="B78" s="5" t="s">
         <v>185</v>
       </c>
@@ -4268,7 +4267,7 @@
       <c r="F78" s="5"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="5" t="s">
         <v>26</v>
       </c>
@@ -4282,7 +4281,7 @@
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
+      <c r="A80" s="15"/>
       <c r="B80" s="5" t="s">
         <v>179</v>
       </c>
@@ -4296,7 +4295,7 @@
       <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
+      <c r="A81" s="15"/>
       <c r="B81" s="5" t="s">
         <v>48</v>
       </c>
@@ -4310,7 +4309,7 @@
       <c r="F81" s="5"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
+      <c r="A82" s="15"/>
       <c r="B82" s="5" t="s">
         <v>29</v>
       </c>
@@ -4324,21 +4323,21 @@
       <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
+      <c r="A83" s="15"/>
       <c r="B83" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C83" s="5">
         <v>500</v>
       </c>
-      <c r="D83" s="16" t="s">
+      <c r="D83" s="13" t="s">
         <v>199</v>
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
+      <c r="A84" s="15"/>
       <c r="B84" s="5" t="s">
         <v>32</v>
       </c>
@@ -4352,21 +4351,21 @@
       <c r="F84" s="5"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
+      <c r="A85" s="15"/>
       <c r="B85" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C85" s="5">
         <v>53.7</v>
       </c>
-      <c r="D85" s="14" t="s">
+      <c r="D85" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
+      <c r="A86" s="15"/>
       <c r="B86" s="5" t="s">
         <v>34</v>
       </c>
@@ -4380,21 +4379,21 @@
       <c r="F86" s="5"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
+      <c r="A87" s="15"/>
       <c r="B87" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C87" s="5">
         <v>22</v>
       </c>
-      <c r="D87" s="14" t="s">
+      <c r="D87" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
+      <c r="A88" s="15"/>
       <c r="B88" s="5" t="s">
         <v>36</v>
       </c>
@@ -4408,21 +4407,21 @@
       <c r="F88" s="5"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="13"/>
+      <c r="A89" s="15"/>
       <c r="B89" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C89" s="5">
         <v>4.2</v>
       </c>
-      <c r="D89" s="14" t="s">
+      <c r="D89" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="13"/>
+      <c r="A90" s="15"/>
       <c r="B90" s="5" t="s">
         <v>38</v>
       </c>
@@ -4436,7 +4435,7 @@
       <c r="F90" s="5"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="13"/>
+      <c r="A91" s="15"/>
       <c r="B91" s="5" t="s">
         <v>39</v>
       </c>
@@ -4450,7 +4449,7 @@
       <c r="F91" s="5"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="13"/>
+      <c r="A92" s="15"/>
       <c r="B92" s="5" t="s">
         <v>40</v>
       </c>
@@ -4464,21 +4463,21 @@
       <c r="F92" s="5"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="13"/>
+      <c r="A93" s="15"/>
       <c r="B93" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C93" s="5">
         <v>1.6</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D93" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="13"/>
+      <c r="A94" s="15"/>
       <c r="B94" s="5" t="s">
         <v>42</v>
       </c>
@@ -4492,7 +4491,7 @@
       <c r="F94" s="5"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="13"/>
+      <c r="A95" s="15"/>
       <c r="B95" s="5" t="s">
         <v>43</v>
       </c>
@@ -4534,7 +4533,7 @@
       <c r="F97" s="5"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="12" t="s">
+      <c r="A98" s="14" t="s">
         <v>138</v>
       </c>
       <c r="B98" t="s">
@@ -4548,7 +4547,7 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="12"/>
+      <c r="A99" s="14"/>
       <c r="B99" t="s">
         <v>122</v>
       </c>
@@ -4560,7 +4559,7 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
+      <c r="A100" s="14"/>
       <c r="B100" t="s">
         <v>59</v>
       </c>
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="12"/>
+      <c r="A101" s="14"/>
       <c r="B101" t="s">
         <v>16</v>
       </c>
@@ -4584,7 +4583,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="12"/>
+      <c r="A102" s="14"/>
       <c r="B102" t="s">
         <v>18</v>
       </c>
@@ -4596,7 +4595,7 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="12"/>
+      <c r="A103" s="14"/>
       <c r="B103" t="s">
         <v>20</v>
       </c>
@@ -4608,7 +4607,7 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="12"/>
+      <c r="A104" s="14"/>
       <c r="B104" t="s">
         <v>21</v>
       </c>
@@ -4620,7 +4619,7 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="12"/>
+      <c r="A105" s="14"/>
       <c r="B105" t="s">
         <v>22</v>
       </c>
@@ -4632,7 +4631,7 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="12"/>
+      <c r="A106" s="14"/>
       <c r="B106" t="s">
         <v>23</v>
       </c>
@@ -4644,7 +4643,7 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="12"/>
+      <c r="A107" s="14"/>
       <c r="B107" t="s">
         <v>24</v>
       </c>
@@ -4656,7 +4655,7 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="12"/>
+      <c r="A108" s="14"/>
       <c r="B108" t="s">
         <v>185</v>
       </c>
@@ -4668,7 +4667,7 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="12"/>
+      <c r="A109" s="14"/>
       <c r="B109" t="s">
         <v>26</v>
       </c>
@@ -4680,7 +4679,7 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="12"/>
+      <c r="A110" s="14"/>
       <c r="B110" t="s">
         <v>179</v>
       </c>
@@ -4692,7 +4691,7 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="12"/>
+      <c r="A111" s="14"/>
       <c r="B111" t="s">
         <v>48</v>
       </c>
@@ -4704,7 +4703,7 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="12"/>
+      <c r="A112" s="14"/>
       <c r="B112" t="s">
         <v>29</v>
       </c>
@@ -4716,7 +4715,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="12"/>
+      <c r="A113" s="14"/>
       <c r="B113" t="s">
         <v>49</v>
       </c>
@@ -4728,7 +4727,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="12"/>
+      <c r="A114" s="14"/>
       <c r="B114" t="s">
         <v>32</v>
       </c>
@@ -4740,19 +4739,19 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="12"/>
+      <c r="A115" s="14"/>
       <c r="B115" t="s">
         <v>33</v>
       </c>
       <c r="C115">
         <v>53.7</v>
       </c>
-      <c r="D115" s="14" t="s">
+      <c r="D115" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="12"/>
+      <c r="A116" s="14"/>
       <c r="B116" t="s">
         <v>34</v>
       </c>
@@ -4764,19 +4763,19 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="12"/>
+      <c r="A117" s="14"/>
       <c r="B117" t="s">
         <v>35</v>
       </c>
       <c r="C117">
         <v>22</v>
       </c>
-      <c r="D117" s="14" t="s">
+      <c r="D117" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="12"/>
+      <c r="A118" s="14"/>
       <c r="B118" t="s">
         <v>36</v>
       </c>
@@ -4788,19 +4787,19 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="12"/>
+      <c r="A119" s="14"/>
       <c r="B119" t="s">
         <v>50</v>
       </c>
       <c r="C119">
         <v>4.2</v>
       </c>
-      <c r="D119" s="14" t="s">
+      <c r="D119" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="12"/>
+      <c r="A120" s="14"/>
       <c r="B120" t="s">
         <v>38</v>
       </c>
@@ -4812,7 +4811,7 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="12"/>
+      <c r="A121" s="14"/>
       <c r="B121" t="s">
         <v>39</v>
       </c>
@@ -4824,7 +4823,7 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="12"/>
+      <c r="A122" s="14"/>
       <c r="B122" t="s">
         <v>40</v>
       </c>
@@ -4836,19 +4835,19 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="12"/>
+      <c r="A123" s="14"/>
       <c r="B123" t="s">
         <v>41</v>
       </c>
       <c r="C123">
         <v>1.6</v>
       </c>
-      <c r="D123" s="14" t="s">
+      <c r="D123" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="12"/>
+      <c r="A124" s="14"/>
       <c r="B124" t="s">
         <v>42</v>
       </c>
@@ -4860,7 +4859,7 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="12"/>
+      <c r="A125" s="14"/>
       <c r="B125" t="s">
         <v>43</v>
       </c>
@@ -4896,7 +4895,7 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="13" t="s">
+      <c r="A128" s="15" t="s">
         <v>144</v>
       </c>
       <c r="B128" s="5" t="s">
@@ -4912,7 +4911,7 @@
       <c r="F128" s="5"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="13"/>
+      <c r="A129" s="15"/>
       <c r="B129" s="5" t="s">
         <v>122</v>
       </c>
@@ -4926,7 +4925,7 @@
       <c r="F129" s="5"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="13"/>
+      <c r="A130" s="15"/>
       <c r="B130" s="5" t="s">
         <v>59</v>
       </c>
@@ -4940,7 +4939,7 @@
       <c r="F130" s="5"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="13"/>
+      <c r="A131" s="15"/>
       <c r="B131" s="5" t="s">
         <v>16</v>
       </c>
@@ -4954,7 +4953,7 @@
       <c r="F131" s="5"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="13"/>
+      <c r="A132" s="15"/>
       <c r="B132" s="5" t="s">
         <v>18</v>
       </c>
@@ -4968,7 +4967,7 @@
       <c r="F132" s="5"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="13"/>
+      <c r="A133" s="15"/>
       <c r="B133" s="5" t="s">
         <v>20</v>
       </c>
@@ -4982,7 +4981,7 @@
       <c r="F133" s="5"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="13"/>
+      <c r="A134" s="15"/>
       <c r="B134" s="5" t="s">
         <v>21</v>
       </c>
@@ -4996,7 +4995,7 @@
       <c r="F134" s="5"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="13"/>
+      <c r="A135" s="15"/>
       <c r="B135" s="5" t="s">
         <v>22</v>
       </c>
@@ -5010,7 +5009,7 @@
       <c r="F135" s="5"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="13"/>
+      <c r="A136" s="15"/>
       <c r="B136" s="5" t="s">
         <v>23</v>
       </c>
@@ -5024,7 +5023,7 @@
       <c r="F136" s="5"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="13"/>
+      <c r="A137" s="15"/>
       <c r="B137" s="5" t="s">
         <v>24</v>
       </c>
@@ -5038,7 +5037,7 @@
       <c r="F137" s="5"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="13"/>
+      <c r="A138" s="15"/>
       <c r="B138" s="5" t="s">
         <v>185</v>
       </c>
@@ -5052,7 +5051,7 @@
       <c r="F138" s="5"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="13"/>
+      <c r="A139" s="15"/>
       <c r="B139" s="5" t="s">
         <v>26</v>
       </c>
@@ -5066,7 +5065,7 @@
       <c r="F139" s="5"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="13"/>
+      <c r="A140" s="15"/>
       <c r="B140" s="5" t="s">
         <v>179</v>
       </c>
@@ -5080,7 +5079,7 @@
       <c r="F140" s="5"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="13"/>
+      <c r="A141" s="15"/>
       <c r="B141" s="5" t="s">
         <v>48</v>
       </c>
@@ -5094,7 +5093,7 @@
       <c r="F141" s="5"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="13"/>
+      <c r="A142" s="15"/>
       <c r="B142" s="5" t="s">
         <v>29</v>
       </c>
@@ -5108,21 +5107,21 @@
       <c r="F142" s="5"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="13"/>
+      <c r="A143" s="15"/>
       <c r="B143" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C143" s="5">
         <v>500</v>
       </c>
-      <c r="D143" s="16" t="s">
+      <c r="D143" s="13" t="s">
         <v>156</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="13"/>
+      <c r="A144" s="15"/>
       <c r="B144" s="5" t="s">
         <v>32</v>
       </c>
@@ -5136,21 +5135,21 @@
       <c r="F144" s="5"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="13"/>
+      <c r="A145" s="15"/>
       <c r="B145" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C145" s="5">
         <v>53.7</v>
       </c>
-      <c r="D145" s="14" t="s">
+      <c r="D145" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="13"/>
+      <c r="A146" s="15"/>
       <c r="B146" s="5" t="s">
         <v>34</v>
       </c>
@@ -5164,21 +5163,21 @@
       <c r="F146" s="5"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="13"/>
+      <c r="A147" s="15"/>
       <c r="B147" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C147" s="5">
         <v>22</v>
       </c>
-      <c r="D147" s="14" t="s">
+      <c r="D147" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="13"/>
+      <c r="A148" s="15"/>
       <c r="B148" s="5" t="s">
         <v>36</v>
       </c>
@@ -5192,21 +5191,21 @@
       <c r="F148" s="5"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="13"/>
+      <c r="A149" s="15"/>
       <c r="B149" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C149" s="5">
         <v>4.2</v>
       </c>
-      <c r="D149" s="14" t="s">
+      <c r="D149" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="13"/>
+      <c r="A150" s="15"/>
       <c r="B150" s="5" t="s">
         <v>38</v>
       </c>
@@ -5220,7 +5219,7 @@
       <c r="F150" s="5"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="13"/>
+      <c r="A151" s="15"/>
       <c r="B151" s="5" t="s">
         <v>39</v>
       </c>
@@ -5234,7 +5233,7 @@
       <c r="F151" s="5"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="13"/>
+      <c r="A152" s="15"/>
       <c r="B152" s="5" t="s">
         <v>40</v>
       </c>
@@ -5248,21 +5247,21 @@
       <c r="F152" s="5"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="13"/>
+      <c r="A153" s="15"/>
       <c r="B153" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C153" s="5">
         <v>1.6</v>
       </c>
-      <c r="D153" s="14" t="s">
+      <c r="D153" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="13"/>
+      <c r="A154" s="15"/>
       <c r="B154" s="5" t="s">
         <v>42</v>
       </c>
@@ -5276,7 +5275,7 @@
       <c r="F154" s="5"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="13"/>
+      <c r="A155" s="15"/>
       <c r="B155" s="5" t="s">
         <v>43</v>
       </c>
@@ -5318,7 +5317,7 @@
       <c r="F157" s="5"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="12" t="s">
+      <c r="A158" s="14" t="s">
         <v>145</v>
       </c>
       <c r="B158" t="s">
@@ -5332,7 +5331,7 @@
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="12"/>
+      <c r="A159" s="14"/>
       <c r="B159" t="s">
         <v>122</v>
       </c>
@@ -5344,7 +5343,7 @@
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="12"/>
+      <c r="A160" s="14"/>
       <c r="B160" t="s">
         <v>59</v>
       </c>
@@ -5356,7 +5355,7 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="12"/>
+      <c r="A161" s="14"/>
       <c r="B161" t="s">
         <v>16</v>
       </c>
@@ -5368,7 +5367,7 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="12"/>
+      <c r="A162" s="14"/>
       <c r="B162" t="s">
         <v>18</v>
       </c>
@@ -5380,7 +5379,7 @@
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="12"/>
+      <c r="A163" s="14"/>
       <c r="B163" t="s">
         <v>20</v>
       </c>
@@ -5392,7 +5391,7 @@
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="12"/>
+      <c r="A164" s="14"/>
       <c r="B164" t="s">
         <v>21</v>
       </c>
@@ -5404,7 +5403,7 @@
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="12"/>
+      <c r="A165" s="14"/>
       <c r="B165" t="s">
         <v>22</v>
       </c>
@@ -5416,7 +5415,7 @@
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="12"/>
+      <c r="A166" s="14"/>
       <c r="B166" t="s">
         <v>23</v>
       </c>
@@ -5428,7 +5427,7 @@
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="12"/>
+      <c r="A167" s="14"/>
       <c r="B167" t="s">
         <v>24</v>
       </c>
@@ -5440,7 +5439,7 @@
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="12"/>
+      <c r="A168" s="14"/>
       <c r="B168" t="s">
         <v>185</v>
       </c>
@@ -5452,7 +5451,7 @@
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="12"/>
+      <c r="A169" s="14"/>
       <c r="B169" t="s">
         <v>26</v>
       </c>
@@ -5464,7 +5463,7 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="12"/>
+      <c r="A170" s="14"/>
       <c r="B170" t="s">
         <v>179</v>
       </c>
@@ -5476,7 +5475,7 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="12"/>
+      <c r="A171" s="14"/>
       <c r="B171" t="s">
         <v>48</v>
       </c>
@@ -5488,7 +5487,7 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="12"/>
+      <c r="A172" s="14"/>
       <c r="B172" t="s">
         <v>29</v>
       </c>
@@ -5500,7 +5499,7 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="12"/>
+      <c r="A173" s="14"/>
       <c r="B173" t="s">
         <v>49</v>
       </c>
@@ -5512,7 +5511,7 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="12"/>
+      <c r="A174" s="14"/>
       <c r="B174" t="s">
         <v>32</v>
       </c>
@@ -5524,19 +5523,19 @@
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="12"/>
+      <c r="A175" s="14"/>
       <c r="B175" t="s">
         <v>33</v>
       </c>
       <c r="C175">
         <v>53.7</v>
       </c>
-      <c r="D175" s="14" t="s">
+      <c r="D175" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="12"/>
+      <c r="A176" s="14"/>
       <c r="B176" t="s">
         <v>34</v>
       </c>
@@ -5548,19 +5547,19 @@
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="12"/>
+      <c r="A177" s="14"/>
       <c r="B177" t="s">
         <v>35</v>
       </c>
       <c r="C177">
         <v>22</v>
       </c>
-      <c r="D177" s="14" t="s">
+      <c r="D177" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="12"/>
+      <c r="A178" s="14"/>
       <c r="B178" t="s">
         <v>36</v>
       </c>
@@ -5572,19 +5571,19 @@
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="12"/>
+      <c r="A179" s="14"/>
       <c r="B179" t="s">
         <v>50</v>
       </c>
       <c r="C179">
         <v>4.2</v>
       </c>
-      <c r="D179" s="14" t="s">
+      <c r="D179" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="12"/>
+      <c r="A180" s="14"/>
       <c r="B180" t="s">
         <v>38</v>
       </c>
@@ -5596,7 +5595,7 @@
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="12"/>
+      <c r="A181" s="14"/>
       <c r="B181" t="s">
         <v>39</v>
       </c>
@@ -5608,7 +5607,7 @@
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="12"/>
+      <c r="A182" s="14"/>
       <c r="B182" t="s">
         <v>40</v>
       </c>
@@ -5620,19 +5619,19 @@
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="12"/>
+      <c r="A183" s="14"/>
       <c r="B183" t="s">
         <v>41</v>
       </c>
       <c r="C183">
         <v>1.6</v>
       </c>
-      <c r="D183" s="14" t="s">
+      <c r="D183" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="12"/>
+      <c r="A184" s="14"/>
       <c r="B184" t="s">
         <v>42</v>
       </c>
@@ -5644,7 +5643,7 @@
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="12"/>
+      <c r="A185" s="14"/>
       <c r="B185" t="s">
         <v>43</v>
       </c>
@@ -5680,7 +5679,7 @@
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="13" t="s">
+      <c r="A188" s="15" t="s">
         <v>150</v>
       </c>
       <c r="B188" s="5" t="s">
@@ -5696,7 +5695,7 @@
       <c r="F188" s="5"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="13"/>
+      <c r="A189" s="15"/>
       <c r="B189" s="5" t="s">
         <v>122</v>
       </c>
@@ -5710,7 +5709,7 @@
       <c r="F189" s="5"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="13"/>
+      <c r="A190" s="15"/>
       <c r="B190" s="5" t="s">
         <v>59</v>
       </c>
@@ -5724,7 +5723,7 @@
       <c r="F190" s="5"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="13"/>
+      <c r="A191" s="15"/>
       <c r="B191" s="5" t="s">
         <v>16</v>
       </c>
@@ -5738,7 +5737,7 @@
       <c r="F191" s="5"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="13"/>
+      <c r="A192" s="15"/>
       <c r="B192" s="5" t="s">
         <v>18</v>
       </c>
@@ -5752,7 +5751,7 @@
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="13"/>
+      <c r="A193" s="15"/>
       <c r="B193" s="5" t="s">
         <v>20</v>
       </c>
@@ -5766,7 +5765,7 @@
       <c r="F193" s="5"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="13"/>
+      <c r="A194" s="15"/>
       <c r="B194" s="5" t="s">
         <v>21</v>
       </c>
@@ -5780,7 +5779,7 @@
       <c r="F194" s="5"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" s="13"/>
+      <c r="A195" s="15"/>
       <c r="B195" s="5" t="s">
         <v>22</v>
       </c>
@@ -5794,7 +5793,7 @@
       <c r="F195" s="5"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="13"/>
+      <c r="A196" s="15"/>
       <c r="B196" s="5" t="s">
         <v>23</v>
       </c>
@@ -5808,7 +5807,7 @@
       <c r="F196" s="5"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="13"/>
+      <c r="A197" s="15"/>
       <c r="B197" s="5" t="s">
         <v>24</v>
       </c>
@@ -5822,7 +5821,7 @@
       <c r="F197" s="5"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="13"/>
+      <c r="A198" s="15"/>
       <c r="B198" s="5" t="s">
         <v>185</v>
       </c>
@@ -5836,7 +5835,7 @@
       <c r="F198" s="5"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="13"/>
+      <c r="A199" s="15"/>
       <c r="B199" s="5" t="s">
         <v>26</v>
       </c>
@@ -5850,7 +5849,7 @@
       <c r="F199" s="5"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="13"/>
+      <c r="A200" s="15"/>
       <c r="B200" s="5" t="s">
         <v>179</v>
       </c>
@@ -5864,7 +5863,7 @@
       <c r="F200" s="5"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="13"/>
+      <c r="A201" s="15"/>
       <c r="B201" s="5" t="s">
         <v>48</v>
       </c>
@@ -5878,7 +5877,7 @@
       <c r="F201" s="5"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="13"/>
+      <c r="A202" s="15"/>
       <c r="B202" s="5" t="s">
         <v>29</v>
       </c>
@@ -5892,7 +5891,7 @@
       <c r="F202" s="5"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="13"/>
+      <c r="A203" s="15"/>
       <c r="B203" s="5" t="s">
         <v>49</v>
       </c>
@@ -5906,7 +5905,7 @@
       <c r="F203" s="5"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="13"/>
+      <c r="A204" s="15"/>
       <c r="B204" s="5" t="s">
         <v>32</v>
       </c>
@@ -5920,21 +5919,21 @@
       <c r="F204" s="5"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="13"/>
+      <c r="A205" s="15"/>
       <c r="B205" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C205" s="5">
         <v>53.7</v>
       </c>
-      <c r="D205" s="14" t="s">
+      <c r="D205" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E205" s="5"/>
       <c r="F205" s="5"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="13"/>
+      <c r="A206" s="15"/>
       <c r="B206" s="5" t="s">
         <v>34</v>
       </c>
@@ -5948,21 +5947,21 @@
       <c r="F206" s="5"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="13"/>
+      <c r="A207" s="15"/>
       <c r="B207" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C207" s="5">
         <v>22</v>
       </c>
-      <c r="D207" s="14" t="s">
+      <c r="D207" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E207" s="5"/>
       <c r="F207" s="5"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="13"/>
+      <c r="A208" s="15"/>
       <c r="B208" s="5" t="s">
         <v>36</v>
       </c>
@@ -5976,21 +5975,21 @@
       <c r="F208" s="5"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="13"/>
+      <c r="A209" s="15"/>
       <c r="B209" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C209" s="5">
         <v>4.2</v>
       </c>
-      <c r="D209" s="14" t="s">
+      <c r="D209" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E209" s="5"/>
       <c r="F209" s="5"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="13"/>
+      <c r="A210" s="15"/>
       <c r="B210" s="5" t="s">
         <v>38</v>
       </c>
@@ -6004,7 +6003,7 @@
       <c r="F210" s="5"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="13"/>
+      <c r="A211" s="15"/>
       <c r="B211" s="5" t="s">
         <v>39</v>
       </c>
@@ -6018,7 +6017,7 @@
       <c r="F211" s="5"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="13"/>
+      <c r="A212" s="15"/>
       <c r="B212" s="5" t="s">
         <v>40</v>
       </c>
@@ -6032,21 +6031,21 @@
       <c r="F212" s="5"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="13"/>
+      <c r="A213" s="15"/>
       <c r="B213" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C213" s="5">
         <v>1.6</v>
       </c>
-      <c r="D213" s="14" t="s">
+      <c r="D213" s="12" t="s">
         <v>156</v>
       </c>
       <c r="E213" s="5"/>
       <c r="F213" s="5"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="13"/>
+      <c r="A214" s="15"/>
       <c r="B214" s="5" t="s">
         <v>42</v>
       </c>
@@ -6060,7 +6059,7 @@
       <c r="F214" s="5"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="13"/>
+      <c r="A215" s="15"/>
       <c r="B215" s="5" t="s">
         <v>43</v>
       </c>
@@ -6130,7 +6129,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -6150,7 +6149,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
+      <c r="A2" s="14"/>
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -6162,7 +6161,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
+      <c r="A3" s="14"/>
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -6174,7 +6173,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="14"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -6186,7 +6185,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="14"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -6198,7 +6197,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+      <c r="A6" s="14"/>
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -6210,7 +6209,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
+      <c r="A7" s="14"/>
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -6222,7 +6221,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -6238,7 +6237,7 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="5" t="s">
         <v>122</v>
       </c>
@@ -6252,7 +6251,7 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
@@ -6266,7 +6265,7 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
@@ -6280,7 +6279,7 @@
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
@@ -6294,7 +6293,7 @@
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
@@ -6308,7 +6307,7 @@
       <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
@@ -6322,7 +6321,7 @@
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
@@ -6336,7 +6335,7 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
@@ -6350,7 +6349,7 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="5" t="s">
         <v>24</v>
       </c>
@@ -6364,7 +6363,7 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="5" t="s">
         <v>185</v>
       </c>
@@ -6378,7 +6377,7 @@
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="5" t="s">
         <v>26</v>
       </c>
@@ -6392,7 +6391,7 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="5" t="s">
         <v>179</v>
       </c>
@@ -6406,7 +6405,7 @@
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="5" t="s">
         <v>28</v>
       </c>
@@ -6420,7 +6419,7 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
@@ -6434,7 +6433,7 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="5" t="s">
         <v>31</v>
       </c>
@@ -6448,7 +6447,7 @@
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="5" t="s">
         <v>32</v>
       </c>
@@ -6462,7 +6461,7 @@
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
@@ -6476,7 +6475,7 @@
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -6490,7 +6489,7 @@
       <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
@@ -6504,7 +6503,7 @@
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -6518,7 +6517,7 @@
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -6532,7 +6531,7 @@
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
@@ -6546,7 +6545,7 @@
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
@@ -6560,7 +6559,7 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="5" t="s">
         <v>40</v>
       </c>
@@ -6574,7 +6573,7 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="5" t="s">
         <v>41</v>
       </c>
@@ -6588,7 +6587,7 @@
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="5" t="s">
         <v>42</v>
       </c>
@@ -6602,7 +6601,7 @@
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
@@ -6644,7 +6643,7 @@
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B38" t="s">
@@ -6658,11 +6657,11 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
+      <c r="A39" s="14"/>
       <c r="B39" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="15" t="b">
+      <c r="C39" t="b">
         <v>0</v>
       </c>
       <c r="D39" t="b">
@@ -6670,7 +6669,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
+      <c r="A40" s="14"/>
       <c r="B40" t="s">
         <v>59</v>
       </c>
@@ -6682,7 +6681,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
+      <c r="A41" s="14"/>
       <c r="B41" t="s">
         <v>16</v>
       </c>
@@ -6694,7 +6693,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
+      <c r="A42" s="14"/>
       <c r="B42" t="s">
         <v>18</v>
       </c>
@@ -6706,7 +6705,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
+      <c r="A43" s="14"/>
       <c r="B43" t="s">
         <v>20</v>
       </c>
@@ -6718,7 +6717,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
+      <c r="A44" s="14"/>
       <c r="B44" t="s">
         <v>21</v>
       </c>
@@ -6730,7 +6729,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
+      <c r="A45" s="14"/>
       <c r="B45" t="s">
         <v>22</v>
       </c>
@@ -6742,7 +6741,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
+      <c r="A46" s="14"/>
       <c r="B46" t="s">
         <v>23</v>
       </c>
@@ -6754,7 +6753,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+      <c r="A47" s="14"/>
       <c r="B47" t="s">
         <v>24</v>
       </c>
@@ -6766,7 +6765,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+      <c r="A48" s="14"/>
       <c r="B48" t="s">
         <v>185</v>
       </c>
@@ -6778,7 +6777,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+      <c r="A49" s="14"/>
       <c r="B49" t="s">
         <v>26</v>
       </c>
@@ -6787,7 +6786,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+      <c r="A50" s="14"/>
       <c r="B50" t="s">
         <v>48</v>
       </c>
@@ -6796,7 +6795,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+      <c r="A51" s="14"/>
       <c r="B51" t="s">
         <v>29</v>
       </c>
@@ -6805,7 +6804,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+      <c r="A52" s="14"/>
       <c r="B52" t="s">
         <v>49</v>
       </c>
@@ -6814,7 +6813,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="14"/>
       <c r="B53" t="s">
         <v>32</v>
       </c>
@@ -6823,7 +6822,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
+      <c r="A54" s="14"/>
       <c r="B54" t="s">
         <v>33</v>
       </c>
@@ -6832,7 +6831,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+      <c r="A55" s="14"/>
       <c r="B55" t="s">
         <v>34</v>
       </c>
@@ -6841,7 +6840,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+      <c r="A56" s="14"/>
       <c r="B56" t="s">
         <v>35</v>
       </c>
@@ -6850,7 +6849,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+      <c r="A57" s="14"/>
       <c r="B57" t="s">
         <v>36</v>
       </c>
@@ -6859,7 +6858,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+      <c r="A58" s="14"/>
       <c r="B58" t="s">
         <v>50</v>
       </c>
@@ -6868,7 +6867,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+      <c r="A59" s="14"/>
       <c r="B59" t="s">
         <v>38</v>
       </c>
@@ -6877,7 +6876,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
+      <c r="A60" s="14"/>
       <c r="B60" t="s">
         <v>39</v>
       </c>
@@ -6886,7 +6885,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+      <c r="A61" s="14"/>
       <c r="B61" t="s">
         <v>40</v>
       </c>
@@ -6895,7 +6894,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
+      <c r="A62" s="14"/>
       <c r="B62" t="s">
         <v>41</v>
       </c>
@@ -6904,7 +6903,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
+      <c r="A63" s="14"/>
       <c r="B63" t="s">
         <v>42</v>
       </c>
@@ -6913,7 +6912,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
+      <c r="A64" s="14"/>
       <c r="B64" t="s">
         <v>43</v>
       </c>
@@ -6922,7 +6921,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="15" t="s">
         <v>60</v>
       </c>
       <c r="B65" s="5" t="s">
@@ -6936,7 +6935,7 @@
       <c r="F65" s="5"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
+      <c r="A66" s="15"/>
       <c r="B66" s="5" t="s">
         <v>122</v>
       </c>
@@ -6948,7 +6947,7 @@
       <c r="F66" s="5"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
+      <c r="A67" s="15"/>
       <c r="B67" s="5" t="s">
         <v>59</v>
       </c>
@@ -6960,7 +6959,7 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="13"/>
+      <c r="A68" s="15"/>
       <c r="B68" s="5" t="s">
         <v>16</v>
       </c>
@@ -6972,7 +6971,7 @@
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="5" t="s">
         <v>18</v>
       </c>
@@ -6984,7 +6983,7 @@
       <c r="F69" s="5"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="13"/>
+      <c r="A70" s="15"/>
       <c r="B70" s="5" t="s">
         <v>20</v>
       </c>
@@ -6996,7 +6995,7 @@
       <c r="F70" s="5"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="5" t="s">
         <v>21</v>
       </c>
@@ -7008,7 +7007,7 @@
       <c r="F71" s="5"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="5" t="s">
         <v>22</v>
       </c>
@@ -7020,7 +7019,7 @@
       <c r="F72" s="5"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="5" t="s">
         <v>23</v>
       </c>
@@ -7032,7 +7031,7 @@
       <c r="F73" s="5"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
+      <c r="A74" s="15"/>
       <c r="B74" s="5" t="s">
         <v>24</v>
       </c>
@@ -7044,7 +7043,7 @@
       <c r="F74" s="5"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
+      <c r="A75" s="15"/>
       <c r="B75" s="5" t="s">
         <v>26</v>
       </c>
@@ -7056,7 +7055,7 @@
       <c r="F75" s="5"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="5" t="s">
         <v>48</v>
       </c>
@@ -7068,7 +7067,7 @@
       <c r="F76" s="5"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
+      <c r="A77" s="15"/>
       <c r="B77" s="5" t="s">
         <v>29</v>
       </c>
@@ -7080,7 +7079,7 @@
       <c r="F77" s="5"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
+      <c r="A78" s="15"/>
       <c r="B78" s="5" t="s">
         <v>49</v>
       </c>
@@ -7092,7 +7091,7 @@
       <c r="F78" s="5"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="5" t="s">
         <v>32</v>
       </c>
@@ -7104,7 +7103,7 @@
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
+      <c r="A80" s="15"/>
       <c r="B80" s="5" t="s">
         <v>33</v>
       </c>
@@ -7116,7 +7115,7 @@
       <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
+      <c r="A81" s="15"/>
       <c r="B81" s="5" t="s">
         <v>34</v>
       </c>
@@ -7128,7 +7127,7 @@
       <c r="F81" s="5"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
+      <c r="A82" s="15"/>
       <c r="B82" s="5" t="s">
         <v>35</v>
       </c>
@@ -7140,7 +7139,7 @@
       <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
+      <c r="A83" s="15"/>
       <c r="B83" s="5" t="s">
         <v>36</v>
       </c>
@@ -7152,7 +7151,7 @@
       <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
+      <c r="A84" s="15"/>
       <c r="B84" s="5" t="s">
         <v>50</v>
       </c>
@@ -7164,7 +7163,7 @@
       <c r="F84" s="5"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
+      <c r="A85" s="15"/>
       <c r="B85" s="5" t="s">
         <v>38</v>
       </c>
@@ -7176,7 +7175,7 @@
       <c r="F85" s="5"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
+      <c r="A86" s="15"/>
       <c r="B86" s="5" t="s">
         <v>39</v>
       </c>
@@ -7188,7 +7187,7 @@
       <c r="F86" s="5"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
+      <c r="A87" s="15"/>
       <c r="B87" s="5" t="s">
         <v>40</v>
       </c>
@@ -7200,7 +7199,7 @@
       <c r="F87" s="5"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
+      <c r="A88" s="15"/>
       <c r="B88" s="5" t="s">
         <v>41</v>
       </c>
@@ -7212,7 +7211,7 @@
       <c r="F88" s="5"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="13"/>
+      <c r="A89" s="15"/>
       <c r="B89" s="5" t="s">
         <v>42</v>
       </c>
@@ -7224,7 +7223,7 @@
       <c r="F89" s="5"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="13"/>
+      <c r="A90" s="15"/>
       <c r="B90" s="5" t="s">
         <v>43</v>
       </c>
@@ -7236,7 +7235,7 @@
       <c r="F90" s="5"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="12" t="s">
+      <c r="A91" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B91" t="s">
@@ -7247,7 +7246,7 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="12"/>
+      <c r="A92" s="14"/>
       <c r="B92" t="s">
         <v>122</v>
       </c>
@@ -7256,7 +7255,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="12"/>
+      <c r="A93" s="14"/>
       <c r="B93" t="s">
         <v>59</v>
       </c>
@@ -7265,7 +7264,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="12"/>
+      <c r="A94" s="14"/>
       <c r="B94" t="s">
         <v>16</v>
       </c>
@@ -7274,7 +7273,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="12"/>
+      <c r="A95" s="14"/>
       <c r="B95" t="s">
         <v>18</v>
       </c>
@@ -7283,7 +7282,7 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="12"/>
+      <c r="A96" s="14"/>
       <c r="B96" t="s">
         <v>20</v>
       </c>
@@ -7292,7 +7291,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="12"/>
+      <c r="A97" s="14"/>
       <c r="B97" t="s">
         <v>21</v>
       </c>
@@ -7301,7 +7300,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="12"/>
+      <c r="A98" s="14"/>
       <c r="B98" t="s">
         <v>22</v>
       </c>
@@ -7310,7 +7309,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="12"/>
+      <c r="A99" s="14"/>
       <c r="B99" t="s">
         <v>23</v>
       </c>
@@ -7319,7 +7318,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
+      <c r="A100" s="14"/>
       <c r="B100" t="s">
         <v>24</v>
       </c>
@@ -7328,7 +7327,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="12"/>
+      <c r="A101" s="14"/>
       <c r="B101" t="s">
         <v>26</v>
       </c>
@@ -7337,7 +7336,7 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="12"/>
+      <c r="A102" s="14"/>
       <c r="B102" t="s">
         <v>48</v>
       </c>
@@ -7346,7 +7345,7 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="12"/>
+      <c r="A103" s="14"/>
       <c r="B103" t="s">
         <v>29</v>
       </c>
@@ -7355,7 +7354,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="12"/>
+      <c r="A104" s="14"/>
       <c r="B104" t="s">
         <v>49</v>
       </c>
@@ -7364,7 +7363,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="12"/>
+      <c r="A105" s="14"/>
       <c r="B105" t="s">
         <v>32</v>
       </c>
@@ -7373,7 +7372,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="12"/>
+      <c r="A106" s="14"/>
       <c r="B106" t="s">
         <v>33</v>
       </c>
@@ -7382,7 +7381,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="12"/>
+      <c r="A107" s="14"/>
       <c r="B107" t="s">
         <v>34</v>
       </c>
@@ -7391,7 +7390,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="12"/>
+      <c r="A108" s="14"/>
       <c r="B108" t="s">
         <v>35</v>
       </c>
@@ -7400,7 +7399,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="12"/>
+      <c r="A109" s="14"/>
       <c r="B109" t="s">
         <v>36</v>
       </c>
@@ -7409,7 +7408,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="12"/>
+      <c r="A110" s="14"/>
       <c r="B110" t="s">
         <v>50</v>
       </c>
@@ -7418,7 +7417,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="12"/>
+      <c r="A111" s="14"/>
       <c r="B111" t="s">
         <v>38</v>
       </c>
@@ -7427,7 +7426,7 @@
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="12"/>
+      <c r="A112" s="14"/>
       <c r="B112" t="s">
         <v>39</v>
       </c>
@@ -7436,7 +7435,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="12"/>
+      <c r="A113" s="14"/>
       <c r="B113" t="s">
         <v>40</v>
       </c>
@@ -7445,7 +7444,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="12"/>
+      <c r="A114" s="14"/>
       <c r="B114" t="s">
         <v>41</v>
       </c>
@@ -7454,7 +7453,7 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="12"/>
+      <c r="A115" s="14"/>
       <c r="B115" t="s">
         <v>42</v>
       </c>
@@ -7463,7 +7462,7 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="12"/>
+      <c r="A116" s="14"/>
       <c r="B116" t="s">
         <v>43</v>
       </c>
@@ -7472,7 +7471,7 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="13" t="s">
+      <c r="A117" s="15" t="s">
         <v>90</v>
       </c>
       <c r="B117" s="5" t="s">
@@ -7486,7 +7485,7 @@
       <c r="F117" s="5"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="13"/>
+      <c r="A118" s="15"/>
       <c r="B118" s="5" t="s">
         <v>122</v>
       </c>
@@ -7498,7 +7497,7 @@
       <c r="F118" s="5"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="13"/>
+      <c r="A119" s="15"/>
       <c r="B119" s="5" t="s">
         <v>59</v>
       </c>
@@ -7510,7 +7509,7 @@
       <c r="F119" s="5"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="13"/>
+      <c r="A120" s="15"/>
       <c r="B120" s="5" t="s">
         <v>16</v>
       </c>
@@ -7522,7 +7521,7 @@
       <c r="F120" s="5"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="13"/>
+      <c r="A121" s="15"/>
       <c r="B121" s="5" t="s">
         <v>18</v>
       </c>
@@ -7534,7 +7533,7 @@
       <c r="F121" s="5"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="13"/>
+      <c r="A122" s="15"/>
       <c r="B122" s="5" t="s">
         <v>20</v>
       </c>
@@ -7546,7 +7545,7 @@
       <c r="F122" s="5"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="13"/>
+      <c r="A123" s="15"/>
       <c r="B123" s="5" t="s">
         <v>21</v>
       </c>
@@ -7558,7 +7557,7 @@
       <c r="F123" s="5"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="13"/>
+      <c r="A124" s="15"/>
       <c r="B124" s="5" t="s">
         <v>22</v>
       </c>
@@ -7570,7 +7569,7 @@
       <c r="F124" s="5"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="13"/>
+      <c r="A125" s="15"/>
       <c r="B125" s="5" t="s">
         <v>23</v>
       </c>
@@ -7582,7 +7581,7 @@
       <c r="F125" s="5"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="13"/>
+      <c r="A126" s="15"/>
       <c r="B126" s="5" t="s">
         <v>24</v>
       </c>
@@ -7594,7 +7593,7 @@
       <c r="F126" s="5"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="13"/>
+      <c r="A127" s="15"/>
       <c r="B127" s="5" t="s">
         <v>26</v>
       </c>
@@ -7606,7 +7605,7 @@
       <c r="F127" s="5"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="13"/>
+      <c r="A128" s="15"/>
       <c r="B128" s="5" t="s">
         <v>48</v>
       </c>
@@ -7618,7 +7617,7 @@
       <c r="F128" s="5"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="13"/>
+      <c r="A129" s="15"/>
       <c r="B129" s="5" t="s">
         <v>29</v>
       </c>
@@ -7630,7 +7629,7 @@
       <c r="F129" s="5"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="13"/>
+      <c r="A130" s="15"/>
       <c r="B130" s="5" t="s">
         <v>49</v>
       </c>
@@ -7642,7 +7641,7 @@
       <c r="F130" s="5"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="13"/>
+      <c r="A131" s="15"/>
       <c r="B131" s="5" t="s">
         <v>32</v>
       </c>
@@ -7654,7 +7653,7 @@
       <c r="F131" s="5"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="13"/>
+      <c r="A132" s="15"/>
       <c r="B132" s="5" t="s">
         <v>33</v>
       </c>
@@ -7666,7 +7665,7 @@
       <c r="F132" s="5"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="13"/>
+      <c r="A133" s="15"/>
       <c r="B133" s="5" t="s">
         <v>34</v>
       </c>
@@ -7678,7 +7677,7 @@
       <c r="F133" s="5"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="13"/>
+      <c r="A134" s="15"/>
       <c r="B134" s="5" t="s">
         <v>35</v>
       </c>
@@ -7690,7 +7689,7 @@
       <c r="F134" s="5"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="13"/>
+      <c r="A135" s="15"/>
       <c r="B135" s="5" t="s">
         <v>36</v>
       </c>
@@ -7702,7 +7701,7 @@
       <c r="F135" s="5"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="13"/>
+      <c r="A136" s="15"/>
       <c r="B136" s="5" t="s">
         <v>50</v>
       </c>
@@ -7714,7 +7713,7 @@
       <c r="F136" s="5"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="13"/>
+      <c r="A137" s="15"/>
       <c r="B137" s="5" t="s">
         <v>38</v>
       </c>
@@ -7726,7 +7725,7 @@
       <c r="F137" s="5"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="13"/>
+      <c r="A138" s="15"/>
       <c r="B138" s="5" t="s">
         <v>39</v>
       </c>
@@ -7738,7 +7737,7 @@
       <c r="F138" s="5"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="13"/>
+      <c r="A139" s="15"/>
       <c r="B139" s="5" t="s">
         <v>40</v>
       </c>
@@ -7750,7 +7749,7 @@
       <c r="F139" s="5"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="13"/>
+      <c r="A140" s="15"/>
       <c r="B140" s="5" t="s">
         <v>41</v>
       </c>
@@ -7762,7 +7761,7 @@
       <c r="F140" s="5"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="13"/>
+      <c r="A141" s="15"/>
       <c r="B141" s="5" t="s">
         <v>42</v>
       </c>
@@ -7774,7 +7773,7 @@
       <c r="F141" s="5"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="13"/>
+      <c r="A142" s="15"/>
       <c r="B142" s="5" t="s">
         <v>43</v>
       </c>
@@ -7786,7 +7785,7 @@
       <c r="F142" s="5"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="12" t="s">
+      <c r="A143" s="14" t="s">
         <v>92</v>
       </c>
       <c r="B143" t="s">
@@ -7797,7 +7796,7 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="12"/>
+      <c r="A144" s="14"/>
       <c r="B144" t="s">
         <v>122</v>
       </c>
@@ -7806,7 +7805,7 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="12"/>
+      <c r="A145" s="14"/>
       <c r="B145" t="s">
         <v>59</v>
       </c>
@@ -7815,7 +7814,7 @@
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="12"/>
+      <c r="A146" s="14"/>
       <c r="B146" t="s">
         <v>16</v>
       </c>
@@ -7824,7 +7823,7 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="12"/>
+      <c r="A147" s="14"/>
       <c r="B147" t="s">
         <v>18</v>
       </c>
@@ -7833,7 +7832,7 @@
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="12"/>
+      <c r="A148" s="14"/>
       <c r="B148" t="s">
         <v>20</v>
       </c>
@@ -7842,7 +7841,7 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="12"/>
+      <c r="A149" s="14"/>
       <c r="B149" t="s">
         <v>21</v>
       </c>
@@ -7851,7 +7850,7 @@
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="12"/>
+      <c r="A150" s="14"/>
       <c r="B150" t="s">
         <v>22</v>
       </c>
@@ -7860,7 +7859,7 @@
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="12"/>
+      <c r="A151" s="14"/>
       <c r="B151" t="s">
         <v>23</v>
       </c>
@@ -7869,7 +7868,7 @@
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="12"/>
+      <c r="A152" s="14"/>
       <c r="B152" t="s">
         <v>24</v>
       </c>
@@ -7878,7 +7877,7 @@
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="12"/>
+      <c r="A153" s="14"/>
       <c r="B153" t="s">
         <v>26</v>
       </c>
@@ -7887,7 +7886,7 @@
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="12"/>
+      <c r="A154" s="14"/>
       <c r="B154" t="s">
         <v>48</v>
       </c>
@@ -7896,7 +7895,7 @@
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="12"/>
+      <c r="A155" s="14"/>
       <c r="B155" t="s">
         <v>29</v>
       </c>
@@ -7905,7 +7904,7 @@
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="12"/>
+      <c r="A156" s="14"/>
       <c r="B156" t="s">
         <v>49</v>
       </c>
@@ -7914,7 +7913,7 @@
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="12"/>
+      <c r="A157" s="14"/>
       <c r="B157" t="s">
         <v>32</v>
       </c>
@@ -7923,7 +7922,7 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="12"/>
+      <c r="A158" s="14"/>
       <c r="B158" t="s">
         <v>33</v>
       </c>
@@ -7932,7 +7931,7 @@
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="12"/>
+      <c r="A159" s="14"/>
       <c r="B159" t="s">
         <v>34</v>
       </c>
@@ -7941,7 +7940,7 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="12"/>
+      <c r="A160" s="14"/>
       <c r="B160" t="s">
         <v>35</v>
       </c>
@@ -7950,7 +7949,7 @@
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="12"/>
+      <c r="A161" s="14"/>
       <c r="B161" t="s">
         <v>36</v>
       </c>
@@ -7959,7 +7958,7 @@
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="12"/>
+      <c r="A162" s="14"/>
       <c r="B162" t="s">
         <v>50</v>
       </c>
@@ -7968,7 +7967,7 @@
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="12"/>
+      <c r="A163" s="14"/>
       <c r="B163" t="s">
         <v>38</v>
       </c>
@@ -7977,7 +7976,7 @@
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="12"/>
+      <c r="A164" s="14"/>
       <c r="B164" t="s">
         <v>39</v>
       </c>
@@ -7986,7 +7985,7 @@
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="12"/>
+      <c r="A165" s="14"/>
       <c r="B165" t="s">
         <v>40</v>
       </c>
@@ -7995,7 +7994,7 @@
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="12"/>
+      <c r="A166" s="14"/>
       <c r="B166" t="s">
         <v>41</v>
       </c>
@@ -8004,7 +8003,7 @@
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="12"/>
+      <c r="A167" s="14"/>
       <c r="B167" t="s">
         <v>42</v>
       </c>
@@ -8013,7 +8012,7 @@
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="12"/>
+      <c r="A168" s="14"/>
       <c r="B168" t="s">
         <v>43</v>
       </c>
@@ -8022,7 +8021,7 @@
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="13" t="s">
+      <c r="A169" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B169" s="5" t="s">
@@ -8036,7 +8035,7 @@
       <c r="F169" s="5"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="13"/>
+      <c r="A170" s="15"/>
       <c r="B170" s="5" t="s">
         <v>122</v>
       </c>
@@ -8048,7 +8047,7 @@
       <c r="F170" s="5"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="13"/>
+      <c r="A171" s="15"/>
       <c r="B171" s="5" t="s">
         <v>59</v>
       </c>
@@ -8060,7 +8059,7 @@
       <c r="F171" s="5"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="13"/>
+      <c r="A172" s="15"/>
       <c r="B172" s="5" t="s">
         <v>16</v>
       </c>
@@ -8072,7 +8071,7 @@
       <c r="F172" s="5"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="13"/>
+      <c r="A173" s="15"/>
       <c r="B173" s="5" t="s">
         <v>18</v>
       </c>
@@ -8084,7 +8083,7 @@
       <c r="F173" s="5"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="13"/>
+      <c r="A174" s="15"/>
       <c r="B174" s="5" t="s">
         <v>20</v>
       </c>
@@ -8096,7 +8095,7 @@
       <c r="F174" s="5"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="13"/>
+      <c r="A175" s="15"/>
       <c r="B175" s="5" t="s">
         <v>21</v>
       </c>
@@ -8108,7 +8107,7 @@
       <c r="F175" s="5"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="13"/>
+      <c r="A176" s="15"/>
       <c r="B176" s="5" t="s">
         <v>22</v>
       </c>
@@ -8120,7 +8119,7 @@
       <c r="F176" s="5"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="13"/>
+      <c r="A177" s="15"/>
       <c r="B177" s="5" t="s">
         <v>23</v>
       </c>
@@ -8132,7 +8131,7 @@
       <c r="F177" s="5"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="13"/>
+      <c r="A178" s="15"/>
       <c r="B178" s="5" t="s">
         <v>24</v>
       </c>
@@ -8144,7 +8143,7 @@
       <c r="F178" s="5"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="13"/>
+      <c r="A179" s="15"/>
       <c r="B179" s="5" t="s">
         <v>26</v>
       </c>
@@ -8156,7 +8155,7 @@
       <c r="F179" s="5"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="13"/>
+      <c r="A180" s="15"/>
       <c r="B180" s="5" t="s">
         <v>48</v>
       </c>
@@ -8168,7 +8167,7 @@
       <c r="F180" s="5"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="13"/>
+      <c r="A181" s="15"/>
       <c r="B181" s="5" t="s">
         <v>29</v>
       </c>
@@ -8180,7 +8179,7 @@
       <c r="F181" s="5"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="13"/>
+      <c r="A182" s="15"/>
       <c r="B182" s="5" t="s">
         <v>49</v>
       </c>
@@ -8192,7 +8191,7 @@
       <c r="F182" s="5"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="13"/>
+      <c r="A183" s="15"/>
       <c r="B183" s="5" t="s">
         <v>32</v>
       </c>
@@ -8204,7 +8203,7 @@
       <c r="F183" s="5"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="13"/>
+      <c r="A184" s="15"/>
       <c r="B184" s="5" t="s">
         <v>33</v>
       </c>
@@ -8216,7 +8215,7 @@
       <c r="F184" s="5"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="13"/>
+      <c r="A185" s="15"/>
       <c r="B185" s="5" t="s">
         <v>34</v>
       </c>
@@ -8228,7 +8227,7 @@
       <c r="F185" s="5"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="13"/>
+      <c r="A186" s="15"/>
       <c r="B186" s="5" t="s">
         <v>35</v>
       </c>
@@ -8240,7 +8239,7 @@
       <c r="F186" s="5"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="13"/>
+      <c r="A187" s="15"/>
       <c r="B187" s="5" t="s">
         <v>36</v>
       </c>
@@ -8252,7 +8251,7 @@
       <c r="F187" s="5"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="13"/>
+      <c r="A188" s="15"/>
       <c r="B188" s="5" t="s">
         <v>50</v>
       </c>
@@ -8264,7 +8263,7 @@
       <c r="F188" s="5"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="13"/>
+      <c r="A189" s="15"/>
       <c r="B189" s="5" t="s">
         <v>38</v>
       </c>
@@ -8276,7 +8275,7 @@
       <c r="F189" s="5"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="13"/>
+      <c r="A190" s="15"/>
       <c r="B190" s="5" t="s">
         <v>39</v>
       </c>
@@ -8288,7 +8287,7 @@
       <c r="F190" s="5"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="13"/>
+      <c r="A191" s="15"/>
       <c r="B191" s="5" t="s">
         <v>40</v>
       </c>
@@ -8300,7 +8299,7 @@
       <c r="F191" s="5"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="13"/>
+      <c r="A192" s="15"/>
       <c r="B192" s="5" t="s">
         <v>41</v>
       </c>
@@ -8312,7 +8311,7 @@
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="13"/>
+      <c r="A193" s="15"/>
       <c r="B193" s="5" t="s">
         <v>42</v>
       </c>
@@ -8324,7 +8323,7 @@
       <c r="F193" s="5"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="13"/>
+      <c r="A194" s="15"/>
       <c r="B194" s="5" t="s">
         <v>43</v>
       </c>
@@ -8336,7 +8335,7 @@
       <c r="F194" s="5"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" s="12" t="s">
+      <c r="A195" s="14" t="s">
         <v>98</v>
       </c>
       <c r="B195" t="s">
@@ -8347,7 +8346,7 @@
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="12"/>
+      <c r="A196" s="14"/>
       <c r="B196" t="s">
         <v>122</v>
       </c>
@@ -8356,7 +8355,7 @@
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="12"/>
+      <c r="A197" s="14"/>
       <c r="B197" t="s">
         <v>59</v>
       </c>
@@ -8365,7 +8364,7 @@
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="12"/>
+      <c r="A198" s="14"/>
       <c r="B198" t="s">
         <v>16</v>
       </c>
@@ -8374,7 +8373,7 @@
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="12"/>
+      <c r="A199" s="14"/>
       <c r="B199" t="s">
         <v>18</v>
       </c>
@@ -8383,7 +8382,7 @@
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="12"/>
+      <c r="A200" s="14"/>
       <c r="B200" t="s">
         <v>20</v>
       </c>
@@ -8392,7 +8391,7 @@
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="12"/>
+      <c r="A201" s="14"/>
       <c r="B201" t="s">
         <v>21</v>
       </c>
@@ -8401,7 +8400,7 @@
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="12"/>
+      <c r="A202" s="14"/>
       <c r="B202" t="s">
         <v>22</v>
       </c>
@@ -8410,7 +8409,7 @@
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="12"/>
+      <c r="A203" s="14"/>
       <c r="B203" t="s">
         <v>23</v>
       </c>
@@ -8419,7 +8418,7 @@
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="12"/>
+      <c r="A204" s="14"/>
       <c r="B204" t="s">
         <v>24</v>
       </c>
@@ -8428,7 +8427,7 @@
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="12"/>
+      <c r="A205" s="14"/>
       <c r="B205" t="s">
         <v>26</v>
       </c>
@@ -8437,7 +8436,7 @@
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="12"/>
+      <c r="A206" s="14"/>
       <c r="B206" t="s">
         <v>48</v>
       </c>
@@ -8446,7 +8445,7 @@
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="12"/>
+      <c r="A207" s="14"/>
       <c r="B207" t="s">
         <v>29</v>
       </c>
@@ -8455,7 +8454,7 @@
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="12"/>
+      <c r="A208" s="14"/>
       <c r="B208" t="s">
         <v>49</v>
       </c>
@@ -8464,7 +8463,7 @@
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="12"/>
+      <c r="A209" s="14"/>
       <c r="B209" t="s">
         <v>32</v>
       </c>
@@ -8473,7 +8472,7 @@
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="12"/>
+      <c r="A210" s="14"/>
       <c r="B210" t="s">
         <v>33</v>
       </c>
@@ -8482,7 +8481,7 @@
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="12"/>
+      <c r="A211" s="14"/>
       <c r="B211" t="s">
         <v>34</v>
       </c>
@@ -8491,7 +8490,7 @@
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="12"/>
+      <c r="A212" s="14"/>
       <c r="B212" t="s">
         <v>35</v>
       </c>
@@ -8500,7 +8499,7 @@
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="12"/>
+      <c r="A213" s="14"/>
       <c r="B213" t="s">
         <v>36</v>
       </c>
@@ -8509,7 +8508,7 @@
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="12"/>
+      <c r="A214" s="14"/>
       <c r="B214" t="s">
         <v>50</v>
       </c>
@@ -8518,7 +8517,7 @@
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="12"/>
+      <c r="A215" s="14"/>
       <c r="B215" t="s">
         <v>38</v>
       </c>
@@ -8527,7 +8526,7 @@
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="12"/>
+      <c r="A216" s="14"/>
       <c r="B216" t="s">
         <v>39</v>
       </c>
@@ -8536,7 +8535,7 @@
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" s="12"/>
+      <c r="A217" s="14"/>
       <c r="B217" t="s">
         <v>40</v>
       </c>
@@ -8545,7 +8544,7 @@
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="12"/>
+      <c r="A218" s="14"/>
       <c r="B218" t="s">
         <v>41</v>
       </c>
@@ -8554,7 +8553,7 @@
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="12"/>
+      <c r="A219" s="14"/>
       <c r="B219" t="s">
         <v>42</v>
       </c>
@@ -8563,7 +8562,7 @@
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="12"/>
+      <c r="A220" s="14"/>
       <c r="B220" t="s">
         <v>43</v>
       </c>
@@ -8572,7 +8571,7 @@
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="13" t="s">
+      <c r="A221" s="15" t="s">
         <v>101</v>
       </c>
       <c r="B221" s="5" t="s">
@@ -8586,7 +8585,7 @@
       <c r="F221" s="5"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="13"/>
+      <c r="A222" s="15"/>
       <c r="B222" s="5" t="s">
         <v>122</v>
       </c>
@@ -8598,7 +8597,7 @@
       <c r="F222" s="5"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" s="13"/>
+      <c r="A223" s="15"/>
       <c r="B223" s="5" t="s">
         <v>59</v>
       </c>
@@ -8610,7 +8609,7 @@
       <c r="F223" s="5"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" s="13"/>
+      <c r="A224" s="15"/>
       <c r="B224" s="5" t="s">
         <v>16</v>
       </c>
@@ -8622,7 +8621,7 @@
       <c r="F224" s="5"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="13"/>
+      <c r="A225" s="15"/>
       <c r="B225" s="5" t="s">
         <v>18</v>
       </c>
@@ -8634,7 +8633,7 @@
       <c r="F225" s="5"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" s="13"/>
+      <c r="A226" s="15"/>
       <c r="B226" s="5" t="s">
         <v>20</v>
       </c>
@@ -8646,7 +8645,7 @@
       <c r="F226" s="5"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" s="13"/>
+      <c r="A227" s="15"/>
       <c r="B227" s="5" t="s">
         <v>21</v>
       </c>
@@ -8658,7 +8657,7 @@
       <c r="F227" s="5"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228" s="13"/>
+      <c r="A228" s="15"/>
       <c r="B228" s="5" t="s">
         <v>22</v>
       </c>
@@ -8670,7 +8669,7 @@
       <c r="F228" s="5"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A229" s="13"/>
+      <c r="A229" s="15"/>
       <c r="B229" s="5" t="s">
         <v>23</v>
       </c>
@@ -8682,7 +8681,7 @@
       <c r="F229" s="5"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" s="13"/>
+      <c r="A230" s="15"/>
       <c r="B230" s="5" t="s">
         <v>24</v>
       </c>
@@ -8694,7 +8693,7 @@
       <c r="F230" s="5"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231" s="13"/>
+      <c r="A231" s="15"/>
       <c r="B231" s="5" t="s">
         <v>26</v>
       </c>
@@ -8706,7 +8705,7 @@
       <c r="F231" s="5"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232" s="13"/>
+      <c r="A232" s="15"/>
       <c r="B232" s="5" t="s">
         <v>48</v>
       </c>
@@ -8718,7 +8717,7 @@
       <c r="F232" s="5"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" s="13"/>
+      <c r="A233" s="15"/>
       <c r="B233" s="5" t="s">
         <v>29</v>
       </c>
@@ -8730,7 +8729,7 @@
       <c r="F233" s="5"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" s="13"/>
+      <c r="A234" s="15"/>
       <c r="B234" s="5" t="s">
         <v>49</v>
       </c>
@@ -8742,7 +8741,7 @@
       <c r="F234" s="5"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="13"/>
+      <c r="A235" s="15"/>
       <c r="B235" s="5" t="s">
         <v>32</v>
       </c>
@@ -8754,7 +8753,7 @@
       <c r="F235" s="5"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" s="13"/>
+      <c r="A236" s="15"/>
       <c r="B236" s="5" t="s">
         <v>33</v>
       </c>
@@ -8766,7 +8765,7 @@
       <c r="F236" s="5"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237" s="13"/>
+      <c r="A237" s="15"/>
       <c r="B237" s="5" t="s">
         <v>34</v>
       </c>
@@ -8778,7 +8777,7 @@
       <c r="F237" s="5"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238" s="13"/>
+      <c r="A238" s="15"/>
       <c r="B238" s="5" t="s">
         <v>35</v>
       </c>
@@ -8790,7 +8789,7 @@
       <c r="F238" s="5"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" s="13"/>
+      <c r="A239" s="15"/>
       <c r="B239" s="5" t="s">
         <v>36</v>
       </c>
@@ -8802,7 +8801,7 @@
       <c r="F239" s="5"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A240" s="13"/>
+      <c r="A240" s="15"/>
       <c r="B240" s="5" t="s">
         <v>50</v>
       </c>
@@ -8814,7 +8813,7 @@
       <c r="F240" s="5"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A241" s="13"/>
+      <c r="A241" s="15"/>
       <c r="B241" s="5" t="s">
         <v>38</v>
       </c>
@@ -8826,7 +8825,7 @@
       <c r="F241" s="5"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A242" s="13"/>
+      <c r="A242" s="15"/>
       <c r="B242" s="5" t="s">
         <v>39</v>
       </c>
@@ -8838,7 +8837,7 @@
       <c r="F242" s="5"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A243" s="13"/>
+      <c r="A243" s="15"/>
       <c r="B243" s="5" t="s">
         <v>40</v>
       </c>
@@ -8850,7 +8849,7 @@
       <c r="F243" s="5"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A244" s="13"/>
+      <c r="A244" s="15"/>
       <c r="B244" s="5" t="s">
         <v>41</v>
       </c>
@@ -8862,7 +8861,7 @@
       <c r="F244" s="5"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A245" s="13"/>
+      <c r="A245" s="15"/>
       <c r="B245" s="5" t="s">
         <v>42</v>
       </c>
@@ -8874,7 +8873,7 @@
       <c r="F245" s="5"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A246" s="13"/>
+      <c r="A246" s="15"/>
       <c r="B246" s="5" t="s">
         <v>43</v>
       </c>
@@ -8886,7 +8885,7 @@
       <c r="F246" s="5"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A247" s="12" t="s">
+      <c r="A247" s="14" t="s">
         <v>109</v>
       </c>
       <c r="B247" t="s">
@@ -8897,7 +8896,7 @@
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A248" s="12"/>
+      <c r="A248" s="14"/>
       <c r="B248" t="s">
         <v>122</v>
       </c>
@@ -8906,7 +8905,7 @@
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A249" s="12"/>
+      <c r="A249" s="14"/>
       <c r="B249" t="s">
         <v>59</v>
       </c>
@@ -8915,7 +8914,7 @@
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A250" s="12"/>
+      <c r="A250" s="14"/>
       <c r="B250" t="s">
         <v>16</v>
       </c>
@@ -8924,7 +8923,7 @@
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A251" s="12"/>
+      <c r="A251" s="14"/>
       <c r="B251" t="s">
         <v>18</v>
       </c>
@@ -8933,7 +8932,7 @@
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A252" s="12"/>
+      <c r="A252" s="14"/>
       <c r="B252" t="s">
         <v>20</v>
       </c>
@@ -8942,7 +8941,7 @@
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A253" s="12"/>
+      <c r="A253" s="14"/>
       <c r="B253" t="s">
         <v>21</v>
       </c>
@@ -8951,7 +8950,7 @@
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A254" s="12"/>
+      <c r="A254" s="14"/>
       <c r="B254" t="s">
         <v>22</v>
       </c>
@@ -8960,7 +8959,7 @@
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255" s="12"/>
+      <c r="A255" s="14"/>
       <c r="B255" t="s">
         <v>23</v>
       </c>
@@ -8969,7 +8968,7 @@
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" s="12"/>
+      <c r="A256" s="14"/>
       <c r="B256" t="s">
         <v>24</v>
       </c>
@@ -8978,7 +8977,7 @@
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="12"/>
+      <c r="A257" s="14"/>
       <c r="B257" t="s">
         <v>26</v>
       </c>
@@ -8987,7 +8986,7 @@
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="12"/>
+      <c r="A258" s="14"/>
       <c r="B258" t="s">
         <v>48</v>
       </c>
@@ -8996,7 +8995,7 @@
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="12"/>
+      <c r="A259" s="14"/>
       <c r="B259" t="s">
         <v>29</v>
       </c>
@@ -9005,7 +9004,7 @@
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="12"/>
+      <c r="A260" s="14"/>
       <c r="B260" t="s">
         <v>49</v>
       </c>
@@ -9014,7 +9013,7 @@
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="12"/>
+      <c r="A261" s="14"/>
       <c r="B261" t="s">
         <v>32</v>
       </c>
@@ -9023,7 +9022,7 @@
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="12"/>
+      <c r="A262" s="14"/>
       <c r="B262" t="s">
         <v>33</v>
       </c>
@@ -9032,7 +9031,7 @@
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="12"/>
+      <c r="A263" s="14"/>
       <c r="B263" t="s">
         <v>34</v>
       </c>
@@ -9041,7 +9040,7 @@
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="12"/>
+      <c r="A264" s="14"/>
       <c r="B264" t="s">
         <v>35</v>
       </c>
@@ -9050,7 +9049,7 @@
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="12"/>
+      <c r="A265" s="14"/>
       <c r="B265" t="s">
         <v>36</v>
       </c>
@@ -9059,7 +9058,7 @@
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="12"/>
+      <c r="A266" s="14"/>
       <c r="B266" t="s">
         <v>50</v>
       </c>
@@ -9068,7 +9067,7 @@
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="12"/>
+      <c r="A267" s="14"/>
       <c r="B267" t="s">
         <v>38</v>
       </c>
@@ -9077,7 +9076,7 @@
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="12"/>
+      <c r="A268" s="14"/>
       <c r="B268" t="s">
         <v>39</v>
       </c>
@@ -9086,7 +9085,7 @@
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="12"/>
+      <c r="A269" s="14"/>
       <c r="B269" t="s">
         <v>40</v>
       </c>
@@ -9095,7 +9094,7 @@
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" s="12"/>
+      <c r="A270" s="14"/>
       <c r="B270" t="s">
         <v>41</v>
       </c>
@@ -9104,7 +9103,7 @@
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="12"/>
+      <c r="A271" s="14"/>
       <c r="B271" t="s">
         <v>42</v>
       </c>
@@ -9113,7 +9112,7 @@
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" s="12"/>
+      <c r="A272" s="14"/>
       <c r="B272" t="s">
         <v>43</v>
       </c>
@@ -9122,7 +9121,7 @@
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" s="13" t="s">
+      <c r="A273" s="15" t="s">
         <v>111</v>
       </c>
       <c r="B273" s="5" t="s">
@@ -9136,7 +9135,7 @@
       <c r="F273" s="5"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" s="13"/>
+      <c r="A274" s="15"/>
       <c r="B274" s="5" t="s">
         <v>122</v>
       </c>
@@ -9148,7 +9147,7 @@
       <c r="F274" s="5"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" s="13"/>
+      <c r="A275" s="15"/>
       <c r="B275" s="5" t="s">
         <v>59</v>
       </c>
@@ -9160,7 +9159,7 @@
       <c r="F275" s="5"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" s="13"/>
+      <c r="A276" s="15"/>
       <c r="B276" s="5" t="s">
         <v>16</v>
       </c>
@@ -9172,7 +9171,7 @@
       <c r="F276" s="5"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277" s="13"/>
+      <c r="A277" s="15"/>
       <c r="B277" s="5" t="s">
         <v>18</v>
       </c>
@@ -9184,7 +9183,7 @@
       <c r="F277" s="5"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A278" s="13"/>
+      <c r="A278" s="15"/>
       <c r="B278" s="5" t="s">
         <v>20</v>
       </c>
@@ -9196,7 +9195,7 @@
       <c r="F278" s="5"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279" s="13"/>
+      <c r="A279" s="15"/>
       <c r="B279" s="5" t="s">
         <v>21</v>
       </c>
@@ -9208,7 +9207,7 @@
       <c r="F279" s="5"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A280" s="13"/>
+      <c r="A280" s="15"/>
       <c r="B280" s="5" t="s">
         <v>22</v>
       </c>
@@ -9220,7 +9219,7 @@
       <c r="F280" s="5"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A281" s="13"/>
+      <c r="A281" s="15"/>
       <c r="B281" s="5" t="s">
         <v>23</v>
       </c>
@@ -9232,7 +9231,7 @@
       <c r="F281" s="5"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A282" s="13"/>
+      <c r="A282" s="15"/>
       <c r="B282" s="5" t="s">
         <v>24</v>
       </c>
@@ -9244,7 +9243,7 @@
       <c r="F282" s="5"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A283" s="13"/>
+      <c r="A283" s="15"/>
       <c r="B283" s="5" t="s">
         <v>26</v>
       </c>
@@ -9256,7 +9255,7 @@
       <c r="F283" s="5"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A284" s="13"/>
+      <c r="A284" s="15"/>
       <c r="B284" s="5" t="s">
         <v>48</v>
       </c>
@@ -9268,7 +9267,7 @@
       <c r="F284" s="5"/>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A285" s="13"/>
+      <c r="A285" s="15"/>
       <c r="B285" s="5" t="s">
         <v>29</v>
       </c>
@@ -9280,7 +9279,7 @@
       <c r="F285" s="5"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A286" s="13"/>
+      <c r="A286" s="15"/>
       <c r="B286" s="5" t="s">
         <v>49</v>
       </c>
@@ -9292,7 +9291,7 @@
       <c r="F286" s="5"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A287" s="13"/>
+      <c r="A287" s="15"/>
       <c r="B287" s="5" t="s">
         <v>32</v>
       </c>
@@ -9304,7 +9303,7 @@
       <c r="F287" s="5"/>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A288" s="13"/>
+      <c r="A288" s="15"/>
       <c r="B288" s="5" t="s">
         <v>33</v>
       </c>
@@ -9316,7 +9315,7 @@
       <c r="F288" s="5"/>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A289" s="13"/>
+      <c r="A289" s="15"/>
       <c r="B289" s="5" t="s">
         <v>34</v>
       </c>
@@ -9328,7 +9327,7 @@
       <c r="F289" s="5"/>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A290" s="13"/>
+      <c r="A290" s="15"/>
       <c r="B290" s="5" t="s">
         <v>35</v>
       </c>
@@ -9340,7 +9339,7 @@
       <c r="F290" s="5"/>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A291" s="13"/>
+      <c r="A291" s="15"/>
       <c r="B291" s="5" t="s">
         <v>36</v>
       </c>
@@ -9352,7 +9351,7 @@
       <c r="F291" s="5"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A292" s="13"/>
+      <c r="A292" s="15"/>
       <c r="B292" s="5" t="s">
         <v>50</v>
       </c>
@@ -9364,7 +9363,7 @@
       <c r="F292" s="5"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A293" s="13"/>
+      <c r="A293" s="15"/>
       <c r="B293" s="5" t="s">
         <v>38</v>
       </c>
@@ -9376,7 +9375,7 @@
       <c r="F293" s="5"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A294" s="13"/>
+      <c r="A294" s="15"/>
       <c r="B294" s="5" t="s">
         <v>39</v>
       </c>
@@ -9388,7 +9387,7 @@
       <c r="F294" s="5"/>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A295" s="13"/>
+      <c r="A295" s="15"/>
       <c r="B295" s="5" t="s">
         <v>40</v>
       </c>
@@ -9400,7 +9399,7 @@
       <c r="F295" s="5"/>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A296" s="13"/>
+      <c r="A296" s="15"/>
       <c r="B296" s="5" t="s">
         <v>41</v>
       </c>
@@ -9412,7 +9411,7 @@
       <c r="F296" s="5"/>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A297" s="13"/>
+      <c r="A297" s="15"/>
       <c r="B297" s="5" t="s">
         <v>42</v>
       </c>
@@ -9424,7 +9423,7 @@
       <c r="F297" s="5"/>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A298" s="13"/>
+      <c r="A298" s="15"/>
       <c r="B298" s="5" t="s">
         <v>43</v>
       </c>
@@ -9436,7 +9435,7 @@
       <c r="F298" s="5"/>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A299" s="12" t="s">
+      <c r="A299" s="14" t="s">
         <v>114</v>
       </c>
       <c r="B299" t="s">
@@ -9447,7 +9446,7 @@
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A300" s="12"/>
+      <c r="A300" s="14"/>
       <c r="B300" t="s">
         <v>122</v>
       </c>
@@ -9456,7 +9455,7 @@
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" s="12"/>
+      <c r="A301" s="14"/>
       <c r="B301" t="s">
         <v>59</v>
       </c>
@@ -9465,7 +9464,7 @@
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A302" s="12"/>
+      <c r="A302" s="14"/>
       <c r="B302" t="s">
         <v>16</v>
       </c>
@@ -9474,7 +9473,7 @@
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A303" s="12"/>
+      <c r="A303" s="14"/>
       <c r="B303" t="s">
         <v>18</v>
       </c>
@@ -9483,7 +9482,7 @@
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A304" s="12"/>
+      <c r="A304" s="14"/>
       <c r="B304" t="s">
         <v>20</v>
       </c>
@@ -9492,7 +9491,7 @@
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="12"/>
+      <c r="A305" s="14"/>
       <c r="B305" t="s">
         <v>21</v>
       </c>
@@ -9501,7 +9500,7 @@
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" s="12"/>
+      <c r="A306" s="14"/>
       <c r="B306" t="s">
         <v>22</v>
       </c>
@@ -9510,7 +9509,7 @@
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" s="12"/>
+      <c r="A307" s="14"/>
       <c r="B307" t="s">
         <v>23</v>
       </c>
@@ -9519,7 +9518,7 @@
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" s="12"/>
+      <c r="A308" s="14"/>
       <c r="B308" t="s">
         <v>24</v>
       </c>
@@ -9528,7 +9527,7 @@
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="12"/>
+      <c r="A309" s="14"/>
       <c r="B309" t="s">
         <v>26</v>
       </c>
@@ -9537,7 +9536,7 @@
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="12"/>
+      <c r="A310" s="14"/>
       <c r="B310" t="s">
         <v>48</v>
       </c>
@@ -9546,7 +9545,7 @@
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" s="12"/>
+      <c r="A311" s="14"/>
       <c r="B311" t="s">
         <v>29</v>
       </c>
@@ -9555,7 +9554,7 @@
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" s="12"/>
+      <c r="A312" s="14"/>
       <c r="B312" t="s">
         <v>49</v>
       </c>
@@ -9564,7 +9563,7 @@
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" s="12"/>
+      <c r="A313" s="14"/>
       <c r="B313" t="s">
         <v>32</v>
       </c>
@@ -9573,7 +9572,7 @@
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" s="12"/>
+      <c r="A314" s="14"/>
       <c r="B314" t="s">
         <v>33</v>
       </c>
@@ -9582,7 +9581,7 @@
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" s="12"/>
+      <c r="A315" s="14"/>
       <c r="B315" t="s">
         <v>34</v>
       </c>
@@ -9591,7 +9590,7 @@
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" s="12"/>
+      <c r="A316" s="14"/>
       <c r="B316" t="s">
         <v>35</v>
       </c>
@@ -9600,7 +9599,7 @@
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" s="12"/>
+      <c r="A317" s="14"/>
       <c r="B317" t="s">
         <v>36</v>
       </c>
@@ -9609,7 +9608,7 @@
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" s="12"/>
+      <c r="A318" s="14"/>
       <c r="B318" t="s">
         <v>50</v>
       </c>
@@ -9618,7 +9617,7 @@
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" s="12"/>
+      <c r="A319" s="14"/>
       <c r="B319" t="s">
         <v>38</v>
       </c>
@@ -9627,7 +9626,7 @@
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" s="12"/>
+      <c r="A320" s="14"/>
       <c r="B320" t="s">
         <v>39</v>
       </c>
@@ -9636,7 +9635,7 @@
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" s="12"/>
+      <c r="A321" s="14"/>
       <c r="B321" t="s">
         <v>40</v>
       </c>
@@ -9645,7 +9644,7 @@
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" s="12"/>
+      <c r="A322" s="14"/>
       <c r="B322" t="s">
         <v>41</v>
       </c>
@@ -9654,7 +9653,7 @@
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" s="12"/>
+      <c r="A323" s="14"/>
       <c r="B323" t="s">
         <v>42</v>
       </c>
@@ -9663,7 +9662,7 @@
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" s="12"/>
+      <c r="A324" s="14"/>
       <c r="B324" t="s">
         <v>43</v>
       </c>
@@ -9673,12 +9672,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:A7"/>
-    <mergeCell ref="A91:A116"/>
-    <mergeCell ref="A117:A142"/>
-    <mergeCell ref="A65:A90"/>
-    <mergeCell ref="A38:A64"/>
-    <mergeCell ref="A8:A35"/>
     <mergeCell ref="A299:A324"/>
     <mergeCell ref="A143:A168"/>
     <mergeCell ref="A169:A194"/>
@@ -9686,6 +9679,12 @@
     <mergeCell ref="A221:A246"/>
     <mergeCell ref="A247:A272"/>
     <mergeCell ref="A273:A298"/>
+    <mergeCell ref="A1:A7"/>
+    <mergeCell ref="A91:A116"/>
+    <mergeCell ref="A117:A142"/>
+    <mergeCell ref="A65:A90"/>
+    <mergeCell ref="A38:A64"/>
+    <mergeCell ref="A8:A35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9705,7 +9704,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -9725,7 +9724,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
+      <c r="A2" s="14"/>
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -9734,7 +9733,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
+      <c r="A3" s="14"/>
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -9743,7 +9742,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="14"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -9752,7 +9751,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="14"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -9761,7 +9760,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+      <c r="A6" s="14"/>
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -9770,7 +9769,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
+      <c r="A7" s="14"/>
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -9779,7 +9778,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -9793,7 +9792,7 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="5" t="s">
         <v>122</v>
       </c>
@@ -9805,7 +9804,7 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
@@ -9817,7 +9816,7 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
@@ -9829,7 +9828,7 @@
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
@@ -9841,7 +9840,7 @@
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
@@ -9853,7 +9852,7 @@
       <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
@@ -9865,7 +9864,7 @@
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
@@ -9877,7 +9876,7 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
@@ -9889,7 +9888,7 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="5" t="s">
         <v>24</v>
       </c>
@@ -9901,7 +9900,7 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="5" t="s">
         <v>26</v>
       </c>
@@ -9913,7 +9912,7 @@
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="5" t="s">
         <v>28</v>
       </c>
@@ -9925,7 +9924,7 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="5" t="s">
         <v>29</v>
       </c>
@@ -9937,7 +9936,7 @@
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="5" t="s">
         <v>31</v>
       </c>
@@ -9949,7 +9948,7 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="5" t="s">
         <v>32</v>
       </c>
@@ -9961,7 +9960,7 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="5" t="s">
         <v>33</v>
       </c>
@@ -9973,7 +9972,7 @@
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="5" t="s">
         <v>34</v>
       </c>
@@ -9985,7 +9984,7 @@
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="5" t="s">
         <v>35</v>
       </c>
@@ -9997,7 +9996,7 @@
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="5" t="s">
         <v>36</v>
       </c>
@@ -10009,7 +10008,7 @@
       <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="5" t="s">
         <v>37</v>
       </c>
@@ -10021,7 +10020,7 @@
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="5" t="s">
         <v>38</v>
       </c>
@@ -10033,7 +10032,7 @@
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="5" t="s">
         <v>39</v>
       </c>
@@ -10045,7 +10044,7 @@
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="5" t="s">
         <v>40</v>
       </c>
@@ -10057,7 +10056,7 @@
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="5" t="s">
         <v>41</v>
       </c>
@@ -10069,7 +10068,7 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="5" t="s">
         <v>42</v>
       </c>
@@ -10081,7 +10080,7 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
@@ -10093,7 +10092,7 @@
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B34" t="s">
@@ -10104,7 +10103,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
+      <c r="A35" s="14"/>
       <c r="B35" t="s">
         <v>122</v>
       </c>
@@ -10113,7 +10112,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
+      <c r="A36" s="14"/>
       <c r="B36" t="s">
         <v>59</v>
       </c>
@@ -10122,7 +10121,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
+      <c r="A37" s="14"/>
       <c r="B37" t="s">
         <v>16</v>
       </c>
@@ -10131,7 +10130,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
+      <c r="A38" s="14"/>
       <c r="B38" t="s">
         <v>18</v>
       </c>
@@ -10140,7 +10139,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
+      <c r="A39" s="14"/>
       <c r="B39" t="s">
         <v>20</v>
       </c>
@@ -10149,7 +10148,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
+      <c r="A40" s="14"/>
       <c r="B40" t="s">
         <v>21</v>
       </c>
@@ -10158,7 +10157,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
+      <c r="A41" s="14"/>
       <c r="B41" t="s">
         <v>22</v>
       </c>
@@ -10167,7 +10166,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
+      <c r="A42" s="14"/>
       <c r="B42" t="s">
         <v>23</v>
       </c>
@@ -10176,7 +10175,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
+      <c r="A43" s="14"/>
       <c r="B43" t="s">
         <v>24</v>
       </c>
@@ -10185,7 +10184,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
+      <c r="A44" s="14"/>
       <c r="B44" t="s">
         <v>26</v>
       </c>
@@ -10194,7 +10193,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
+      <c r="A45" s="14"/>
       <c r="B45" t="s">
         <v>48</v>
       </c>
@@ -10203,7 +10202,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
+      <c r="A46" s="14"/>
       <c r="B46" t="s">
         <v>29</v>
       </c>
@@ -10212,7 +10211,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+      <c r="A47" s="14"/>
       <c r="B47" t="s">
         <v>49</v>
       </c>
@@ -10221,7 +10220,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+      <c r="A48" s="14"/>
       <c r="B48" t="s">
         <v>32</v>
       </c>
@@ -10230,7 +10229,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+      <c r="A49" s="14"/>
       <c r="B49" t="s">
         <v>33</v>
       </c>
@@ -10239,7 +10238,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+      <c r="A50" s="14"/>
       <c r="B50" t="s">
         <v>34</v>
       </c>
@@ -10248,7 +10247,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+      <c r="A51" s="14"/>
       <c r="B51" t="s">
         <v>35</v>
       </c>
@@ -10257,7 +10256,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+      <c r="A52" s="14"/>
       <c r="B52" t="s">
         <v>36</v>
       </c>
@@ -10266,7 +10265,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="14"/>
       <c r="B53" t="s">
         <v>37</v>
       </c>
@@ -10275,7 +10274,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
+      <c r="A54" s="14"/>
       <c r="B54" t="s">
         <v>38</v>
       </c>
@@ -10284,7 +10283,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+      <c r="A55" s="14"/>
       <c r="B55" t="s">
         <v>39</v>
       </c>
@@ -10293,7 +10292,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+      <c r="A56" s="14"/>
       <c r="B56" t="s">
         <v>40</v>
       </c>
@@ -10302,7 +10301,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+      <c r="A57" s="14"/>
       <c r="B57" t="s">
         <v>41</v>
       </c>
@@ -10311,7 +10310,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+      <c r="A58" s="14"/>
       <c r="B58" t="s">
         <v>42</v>
       </c>
@@ -10320,7 +10319,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+      <c r="A59" s="14"/>
       <c r="B59" t="s">
         <v>43</v>
       </c>
@@ -10329,7 +10328,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="15" t="s">
         <v>60</v>
       </c>
       <c r="B60" s="5" t="s">
@@ -10343,7 +10342,7 @@
       <c r="F60" s="5"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
+      <c r="A61" s="15"/>
       <c r="B61" s="5" t="s">
         <v>122</v>
       </c>
@@ -10355,7 +10354,7 @@
       <c r="F61" s="5"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="13"/>
+      <c r="A62" s="15"/>
       <c r="B62" s="5" t="s">
         <v>59</v>
       </c>
@@ -10367,7 +10366,7 @@
       <c r="F62" s="5"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
+      <c r="A63" s="15"/>
       <c r="B63" s="5" t="s">
         <v>16</v>
       </c>
@@ -10379,7 +10378,7 @@
       <c r="F63" s="5"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="13"/>
+      <c r="A64" s="15"/>
       <c r="B64" s="5" t="s">
         <v>18</v>
       </c>
@@ -10391,7 +10390,7 @@
       <c r="F64" s="5"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
+      <c r="A65" s="15"/>
       <c r="B65" s="5" t="s">
         <v>20</v>
       </c>
@@ -10403,7 +10402,7 @@
       <c r="F65" s="5"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
+      <c r="A66" s="15"/>
       <c r="B66" s="5" t="s">
         <v>21</v>
       </c>
@@ -10415,7 +10414,7 @@
       <c r="F66" s="5"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
+      <c r="A67" s="15"/>
       <c r="B67" s="5" t="s">
         <v>22</v>
       </c>
@@ -10427,7 +10426,7 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="13"/>
+      <c r="A68" s="15"/>
       <c r="B68" s="5" t="s">
         <v>23</v>
       </c>
@@ -10439,7 +10438,7 @@
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
@@ -10451,7 +10450,7 @@
       <c r="F69" s="5"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="13"/>
+      <c r="A70" s="15"/>
       <c r="B70" s="5" t="s">
         <v>26</v>
       </c>
@@ -10463,7 +10462,7 @@
       <c r="F70" s="5"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="5" t="s">
         <v>48</v>
       </c>
@@ -10475,7 +10474,7 @@
       <c r="F71" s="5"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="5" t="s">
         <v>29</v>
       </c>
@@ -10487,7 +10486,7 @@
       <c r="F72" s="5"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="5" t="s">
         <v>49</v>
       </c>
@@ -10499,7 +10498,7 @@
       <c r="F73" s="5"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
+      <c r="A74" s="15"/>
       <c r="B74" s="5" t="s">
         <v>32</v>
       </c>
@@ -10511,7 +10510,7 @@
       <c r="F74" s="5"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
+      <c r="A75" s="15"/>
       <c r="B75" s="5" t="s">
         <v>33</v>
       </c>
@@ -10523,7 +10522,7 @@
       <c r="F75" s="5"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="5" t="s">
         <v>34</v>
       </c>
@@ -10535,7 +10534,7 @@
       <c r="F76" s="5"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
+      <c r="A77" s="15"/>
       <c r="B77" s="5" t="s">
         <v>35</v>
       </c>
@@ -10547,7 +10546,7 @@
       <c r="F77" s="5"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
+      <c r="A78" s="15"/>
       <c r="B78" s="5" t="s">
         <v>36</v>
       </c>
@@ -10559,7 +10558,7 @@
       <c r="F78" s="5"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="5" t="s">
         <v>50</v>
       </c>
@@ -10571,7 +10570,7 @@
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
+      <c r="A80" s="15"/>
       <c r="B80" s="5" t="s">
         <v>38</v>
       </c>
@@ -10583,7 +10582,7 @@
       <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
+      <c r="A81" s="15"/>
       <c r="B81" s="5" t="s">
         <v>39</v>
       </c>
@@ -10595,7 +10594,7 @@
       <c r="F81" s="5"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
+      <c r="A82" s="15"/>
       <c r="B82" s="5" t="s">
         <v>40</v>
       </c>
@@ -10607,7 +10606,7 @@
       <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
+      <c r="A83" s="15"/>
       <c r="B83" s="5" t="s">
         <v>41</v>
       </c>
@@ -10619,7 +10618,7 @@
       <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
+      <c r="A84" s="15"/>
       <c r="B84" s="5" t="s">
         <v>42</v>
       </c>
@@ -10631,7 +10630,7 @@
       <c r="F84" s="5"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
+      <c r="A85" s="15"/>
       <c r="B85" s="5" t="s">
         <v>43</v>
       </c>
@@ -10643,7 +10642,7 @@
       <c r="F85" s="5"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B86" t="s">
@@ -10654,7 +10653,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="12"/>
+      <c r="A87" s="14"/>
       <c r="B87" t="s">
         <v>122</v>
       </c>
@@ -10663,7 +10662,7 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="12"/>
+      <c r="A88" s="14"/>
       <c r="B88" t="s">
         <v>59</v>
       </c>
@@ -10672,7 +10671,7 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="12"/>
+      <c r="A89" s="14"/>
       <c r="B89" t="s">
         <v>16</v>
       </c>
@@ -10681,7 +10680,7 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="12"/>
+      <c r="A90" s="14"/>
       <c r="B90" t="s">
         <v>18</v>
       </c>
@@ -10690,7 +10689,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="12"/>
+      <c r="A91" s="14"/>
       <c r="B91" t="s">
         <v>20</v>
       </c>
@@ -10699,7 +10698,7 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="12"/>
+      <c r="A92" s="14"/>
       <c r="B92" t="s">
         <v>21</v>
       </c>
@@ -10708,7 +10707,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="12"/>
+      <c r="A93" s="14"/>
       <c r="B93" t="s">
         <v>22</v>
       </c>
@@ -10717,7 +10716,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="12"/>
+      <c r="A94" s="14"/>
       <c r="B94" t="s">
         <v>23</v>
       </c>
@@ -10726,7 +10725,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="12"/>
+      <c r="A95" s="14"/>
       <c r="B95" t="s">
         <v>24</v>
       </c>
@@ -10735,7 +10734,7 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="12"/>
+      <c r="A96" s="14"/>
       <c r="B96" t="s">
         <v>26</v>
       </c>
@@ -10744,7 +10743,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="12"/>
+      <c r="A97" s="14"/>
       <c r="B97" t="s">
         <v>48</v>
       </c>
@@ -10753,7 +10752,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="12"/>
+      <c r="A98" s="14"/>
       <c r="B98" t="s">
         <v>29</v>
       </c>
@@ -10762,7 +10761,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="12"/>
+      <c r="A99" s="14"/>
       <c r="B99" t="s">
         <v>49</v>
       </c>
@@ -10771,7 +10770,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
+      <c r="A100" s="14"/>
       <c r="B100" t="s">
         <v>32</v>
       </c>
@@ -10780,7 +10779,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="12"/>
+      <c r="A101" s="14"/>
       <c r="B101" t="s">
         <v>33</v>
       </c>
@@ -10789,7 +10788,7 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="12"/>
+      <c r="A102" s="14"/>
       <c r="B102" t="s">
         <v>34</v>
       </c>
@@ -10798,7 +10797,7 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="12"/>
+      <c r="A103" s="14"/>
       <c r="B103" t="s">
         <v>35</v>
       </c>
@@ -10807,7 +10806,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="12"/>
+      <c r="A104" s="14"/>
       <c r="B104" t="s">
         <v>36</v>
       </c>
@@ -10816,7 +10815,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="12"/>
+      <c r="A105" s="14"/>
       <c r="B105" t="s">
         <v>37</v>
       </c>
@@ -10825,7 +10824,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="12"/>
+      <c r="A106" s="14"/>
       <c r="B106" t="s">
         <v>38</v>
       </c>
@@ -10834,7 +10833,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="12"/>
+      <c r="A107" s="14"/>
       <c r="B107" t="s">
         <v>39</v>
       </c>
@@ -10843,7 +10842,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="12"/>
+      <c r="A108" s="14"/>
       <c r="B108" t="s">
         <v>40</v>
       </c>
@@ -10852,7 +10851,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="12"/>
+      <c r="A109" s="14"/>
       <c r="B109" t="s">
         <v>41</v>
       </c>
@@ -10861,7 +10860,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="12"/>
+      <c r="A110" s="14"/>
       <c r="B110" t="s">
         <v>76</v>
       </c>
@@ -10870,7 +10869,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="12"/>
+      <c r="A111" s="14"/>
       <c r="B111" t="s">
         <v>43</v>
       </c>
